--- a/data/cox_xlsx/BO.CO.xlsx
+++ b/data/cox_xlsx/BO.CO.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="536">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -1060,6 +1060,9 @@
   </si>
   <si>
     <t>Non-current other liabilities</t>
+  </si>
+  <si>
+    <t>Loans from Banks LT</t>
   </si>
   <si>
     <t>Misc other L/T liabs</t>
@@ -1749,7 +1752,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1827,6 +1830,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -17603,8 +17609,8 @@
       <c r="V137" s="19"/>
     </row>
     <row r="138" ht="15.0" customHeight="1">
-      <c r="A138" s="14" t="s">
-        <v>326</v>
+      <c r="A138" s="26" t="s">
+        <v>347</v>
       </c>
       <c r="B138" s="19"/>
       <c r="C138" s="19"/>
@@ -17684,7 +17690,7 @@
     </row>
     <row r="140" ht="15.0" customHeight="1">
       <c r="A140" s="14" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B140" s="19"/>
       <c r="C140" s="19"/>
@@ -17714,7 +17720,7 @@
     </row>
     <row r="141" ht="15.0" customHeight="1">
       <c r="A141" s="14" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B141" s="19"/>
       <c r="C141" s="19"/>
@@ -17744,7 +17750,7 @@
     </row>
     <row r="142" ht="15.0" customHeight="1">
       <c r="A142" s="16" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B142" s="17">
         <v>335.37</v>
@@ -17812,7 +17818,7 @@
     </row>
     <row r="143" ht="15.0" customHeight="1">
       <c r="A143" s="14" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B143" s="19"/>
       <c r="C143" s="19"/>
@@ -17846,7 +17852,7 @@
     </row>
     <row r="144" ht="15.0" customHeight="1">
       <c r="A144" s="14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B144" s="19"/>
       <c r="C144" s="19"/>
@@ -17880,7 +17886,7 @@
     </row>
     <row r="145" ht="15.0" customHeight="1">
       <c r="A145" s="16" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B145" s="17">
         <v>1856.94</v>
@@ -17948,7 +17954,7 @@
     </row>
     <row r="146" ht="15.0" customHeight="1">
       <c r="A146" s="14" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B146" s="15">
         <v>1144.28</v>
@@ -18016,7 +18022,7 @@
     </row>
     <row r="147" ht="15.0" customHeight="1">
       <c r="A147" s="14" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B147" s="18">
         <v>10.87</v>
@@ -18078,7 +18084,7 @@
     </row>
     <row r="148" ht="15.0" customHeight="1">
       <c r="A148" s="14" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B148" s="20">
         <v>-3.11</v>
@@ -18144,7 +18150,7 @@
     </row>
     <row r="149" ht="15.0" customHeight="1">
       <c r="A149" s="14" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B149" s="15">
         <v>624.15</v>
@@ -18212,7 +18218,7 @@
     </row>
     <row r="150" ht="15.0" customHeight="1">
       <c r="A150" s="14" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B150" s="19"/>
       <c r="C150" s="19"/>
@@ -18244,7 +18250,7 @@
     </row>
     <row r="151" ht="15.0" customHeight="1">
       <c r="A151" s="14" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B151" s="19"/>
       <c r="C151" s="19"/>
@@ -18284,7 +18290,7 @@
     </row>
     <row r="152" ht="15.0" customHeight="1">
       <c r="A152" s="14" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B152" s="19"/>
       <c r="C152" s="19"/>
@@ -18316,7 +18322,7 @@
     </row>
     <row r="153" ht="15.0" customHeight="1">
       <c r="A153" s="16" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B153" s="17">
         <v>1776.2</v>
@@ -18468,7 +18474,7 @@
     </row>
     <row r="156" ht="15.0" customHeight="1">
       <c r="A156" s="16" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B156" s="17">
         <v>1776.2</v>
@@ -18536,7 +18542,7 @@
     </row>
     <row r="157" ht="15.0" customHeight="1">
       <c r="A157" s="14" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B157" s="19"/>
       <c r="C157" s="19"/>
@@ -18566,7 +18572,7 @@
     </row>
     <row r="158" ht="15.0" customHeight="1">
       <c r="A158" s="16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B158" s="17">
         <v>3633.14</v>
@@ -18634,7 +18640,7 @@
     </row>
     <row r="159" ht="15.0" customHeight="1">
       <c r="A159" s="14" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B159" s="15">
         <v>144.36</v>
@@ -18702,7 +18708,7 @@
     </row>
     <row r="160" ht="15.0" customHeight="1">
       <c r="A160" s="14" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B160" s="15">
         <v>147.33</v>
@@ -18770,7 +18776,7 @@
     </row>
     <row r="161" ht="15.0" customHeight="1">
       <c r="A161" s="14" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B161" s="18">
         <v>2.96</v>
@@ -18838,7 +18844,7 @@
     </row>
     <row r="162" ht="15.0" customHeight="1">
       <c r="A162" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B162" s="19"/>
       <c r="C162" s="19"/>
@@ -18878,7 +18884,7 @@
     </row>
     <row r="163" ht="15.0" customHeight="1">
       <c r="A163" s="14" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B163" s="19"/>
       <c r="C163" s="19"/>
@@ -18922,7 +18928,7 @@
     </row>
     <row r="164" ht="15.0" customHeight="1">
       <c r="A164" s="14" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B164" s="18">
         <v>4.66</v>
@@ -18988,7 +18994,7 @@
     </row>
     <row r="165" ht="15.0" customHeight="1">
       <c r="A165" s="14" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B165" s="18">
         <v>20.18</v>
@@ -19052,7 +19058,7 @@
     </row>
     <row r="166" ht="15.0" customHeight="1">
       <c r="A166" s="14" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B166" s="18">
         <v>57.45</v>
@@ -19116,7 +19122,7 @@
     </row>
     <row r="167" ht="15.0" customHeight="1">
       <c r="A167" s="14" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B167" s="19"/>
       <c r="C167" s="19"/>
@@ -19156,7 +19162,7 @@
     </row>
     <row r="168" ht="15.0" customHeight="1">
       <c r="A168" s="14" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B168" s="19"/>
       <c r="C168" s="19"/>
@@ -19186,7 +19192,7 @@
     </row>
     <row r="169" ht="15.0" customHeight="1">
       <c r="A169" s="14" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B169" s="18">
         <v>91.6</v>
@@ -19230,7 +19236,7 @@
     </row>
     <row r="170" ht="15.0" customHeight="1">
       <c r="A170" s="14" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B170" s="15">
         <v>155.26</v>
@@ -19274,7 +19280,7 @@
     </row>
     <row r="171" ht="15.0" customHeight="1">
       <c r="A171" s="14" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B171" s="18">
         <v>38.82</v>
@@ -19312,7 +19318,7 @@
     </row>
     <row r="172" ht="15.0" customHeight="1">
       <c r="A172" s="14" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B172" s="15">
         <v>144.36</v>
@@ -19380,7 +19386,7 @@
     </row>
     <row r="173" ht="15.0" customHeight="1">
       <c r="A173" s="14" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B173" s="18">
         <v>2.96</v>
@@ -19448,7 +19454,7 @@
     </row>
     <row r="174" ht="15.0" customHeight="1">
       <c r="A174" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B174" s="15">
         <v>147.33</v>
@@ -19516,7 +19522,7 @@
     </row>
     <row r="175" ht="15.0" customHeight="1">
       <c r="A175" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B175" s="18">
         <v>1.0</v>
@@ -19584,7 +19590,7 @@
     </row>
     <row r="176" ht="15.0" customHeight="1">
       <c r="A176" s="14" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B176" s="19"/>
       <c r="C176" s="19"/>
@@ -19616,7 +19622,7 @@
     </row>
     <row r="177" ht="15.0" customHeight="1">
       <c r="A177" s="14" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B177" s="19"/>
       <c r="C177" s="19"/>
@@ -19650,7 +19656,7 @@
     </row>
     <row r="178" ht="15.0" customHeight="1">
       <c r="A178" s="14" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B178" s="19"/>
       <c r="C178" s="19"/>
@@ -19684,7 +19690,7 @@
     </row>
     <row r="179" ht="15.0" customHeight="1">
       <c r="A179" s="14" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B179" s="19"/>
       <c r="C179" s="19"/>
@@ -20558,7 +20564,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -20931,67 +20937,67 @@
         <v>43</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -21064,7 +21070,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -21158,7 +21164,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B20" s="15">
         <v>383.89</v>
@@ -21268,7 +21274,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="14" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -21308,7 +21314,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="14" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -21348,7 +21354,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B25" s="19"/>
       <c r="C25" s="19"/>
@@ -21388,7 +21394,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B26" s="19"/>
       <c r="C26" s="19"/>
@@ -21428,7 +21434,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B27" s="18">
         <v>73.64</v>
@@ -21534,7 +21540,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B29" s="20">
         <v>-61.11</v>
@@ -21640,7 +21646,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B31" s="20">
         <v>-23.5</v>
@@ -21680,7 +21686,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="14" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B32" s="18">
         <v>81.48</v>
@@ -21786,7 +21792,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
@@ -21822,7 +21828,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B35" s="19"/>
       <c r="C35" s="19"/>
@@ -21850,7 +21856,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B36" s="15">
         <v>100.28</v>
@@ -21918,7 +21924,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B37" s="22">
         <v>-130.05</v>
@@ -21982,7 +21988,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B38" s="20">
         <v>-15.67</v>
@@ -22050,7 +22056,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="14" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B39" s="19"/>
       <c r="C39" s="19"/>
@@ -22154,7 +22160,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
@@ -22212,7 +22218,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B42" s="20">
         <v>-36.04</v>
@@ -22320,7 +22326,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
@@ -22352,7 +22358,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B45" s="19"/>
       <c r="C45" s="19"/>
@@ -22380,7 +22386,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -22412,7 +22418,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B47" s="19"/>
       <c r="C47" s="19"/>
@@ -22456,7 +22462,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B48" s="19"/>
       <c r="C48" s="19"/>
@@ -22486,7 +22492,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
@@ -22518,7 +22524,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
@@ -22550,7 +22556,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B51" s="19"/>
       <c r="C51" s="19"/>
@@ -22580,7 +22586,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
@@ -22610,7 +22616,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B53" s="19"/>
       <c r="C53" s="19"/>
@@ -22638,7 +22644,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B54" s="19"/>
       <c r="C54" s="19"/>
@@ -22668,7 +22674,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="16" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B55" s="17">
         <v>401.13</v>
@@ -22736,7 +22742,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="14" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B56" s="22">
         <v>-313.38</v>
@@ -22804,7 +22810,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B57" s="20">
         <v>-61.11</v>
@@ -22872,7 +22878,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
@@ -22910,7 +22916,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B59" s="19"/>
       <c r="C59" s="19"/>
@@ -22970,7 +22976,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -23010,7 +23016,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B61" s="19"/>
       <c r="C61" s="19"/>
@@ -23050,7 +23056,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B62" s="19"/>
       <c r="C62" s="19"/>
@@ -23084,7 +23090,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B63" s="20">
         <v>-3.13</v>
@@ -23150,7 +23156,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B64" s="19"/>
       <c r="C64" s="19"/>
@@ -23184,7 +23190,7 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="14" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
@@ -23220,7 +23226,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
@@ -23248,7 +23254,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B67" s="19"/>
       <c r="C67" s="19"/>
@@ -23278,7 +23284,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B68" s="19"/>
       <c r="C68" s="19"/>
@@ -23306,7 +23312,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="14" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B69" s="19"/>
       <c r="C69" s="19">
@@ -23340,7 +23346,7 @@
     </row>
     <row r="70" ht="15.0" customHeight="1">
       <c r="A70" s="14" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B70" s="18">
         <v>14.1</v>
@@ -23376,7 +23382,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B71" s="18">
         <v>1.57</v>
@@ -23414,7 +23420,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="16" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B72" s="24">
         <v>-361.95</v>
@@ -23482,7 +23488,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
@@ -23514,7 +23520,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B74" s="20">
         <v>-72.08</v>
@@ -23552,7 +23558,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="14" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B75" s="20">
         <v>-4.7</v>
@@ -23620,7 +23626,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="14" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B76" s="20">
         <v>-31.34</v>
@@ -23680,7 +23686,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B77" s="19"/>
       <c r="C77" s="19">
@@ -23710,7 +23716,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="14" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B78" s="15">
         <v>340.02</v>
@@ -23742,7 +23748,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B79" s="19"/>
       <c r="C79" s="19"/>
@@ -23790,7 +23796,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B80" s="19"/>
       <c r="C80" s="19"/>
@@ -23828,7 +23834,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
@@ -23856,7 +23862,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B82" s="19"/>
       <c r="C82" s="19"/>
@@ -23892,7 +23898,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B83" s="19"/>
       <c r="C83" s="19"/>
@@ -23922,7 +23928,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B84" s="19"/>
       <c r="C84" s="19"/>
@@ -23960,7 +23966,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B85" s="19"/>
       <c r="C85" s="19"/>
@@ -24008,7 +24014,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B86" s="19"/>
       <c r="C86" s="19"/>
@@ -24042,7 +24048,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B87" s="19"/>
       <c r="C87" s="19"/>
@@ -24082,7 +24088,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B88" s="19"/>
       <c r="C88" s="19"/>
@@ -24112,7 +24118,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="14" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
@@ -24140,7 +24146,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B90" s="19"/>
       <c r="C90" s="19"/>
@@ -24170,7 +24176,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="14" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B91" s="19"/>
       <c r="C91" s="19"/>
@@ -24198,7 +24204,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="14" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B92" s="19"/>
       <c r="C92" s="19"/>
@@ -24230,7 +24236,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="14" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B93" s="22">
         <v>-322.78</v>
@@ -24258,7 +24264,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B94" s="19"/>
       <c r="C94" s="20">
@@ -24290,7 +24296,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="16" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B95" s="25">
         <v>-90.88</v>
@@ -24358,7 +24364,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B96" s="19"/>
       <c r="C96" s="19"/>
@@ -24398,7 +24404,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B97" s="15">
         <v>274.81</v>
@@ -24466,7 +24472,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B98" s="15">
         <v>225.13</v>
@@ -24534,7 +24540,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B99" s="19"/>
       <c r="C99" s="19"/>
@@ -24572,7 +24578,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B100" s="20">
         <v>-1.57</v>
@@ -24602,7 +24608,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B101" s="18">
         <v>1.57</v>
@@ -24638,7 +24644,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="16" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B102" s="25">
         <v>-51.71</v>
@@ -24706,7 +24712,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B103" s="18">
         <v>25.07</v>
@@ -25658,7 +25664,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -25834,40 +25840,40 @@
         <v>38</v>
       </c>
       <c r="W11" s="7" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="X11" s="7" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Y11" s="7" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="Z11" s="7" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AA11" s="7" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AB11" s="7" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AC11" s="7" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AG11" s="7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AH11" s="7" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="12" ht="15.0" customHeight="1" outlineLevel="1">
@@ -26392,7 +26398,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -26496,3997 +26502,3997 @@
         <v>69</v>
       </c>
       <c r="W19" s="13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="X19" s="13" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="Y19" s="13" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA19" s="13" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AB19" s="13" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AC19" s="13" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AD19" s="13" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AE19" s="13" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AF19" s="13" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG19" s="13" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AH19" s="13" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="26" t="s">
-        <v>484</v>
-      </c>
-      <c r="B20" s="27"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27"/>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="27"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="27"/>
-      <c r="Z20" s="27"/>
-      <c r="AA20" s="27"/>
-      <c r="AB20" s="27"/>
-      <c r="AC20" s="27"/>
-      <c r="AD20" s="27"/>
-      <c r="AE20" s="27"/>
-      <c r="AF20" s="27"/>
-      <c r="AG20" s="27"/>
-      <c r="AH20" s="27"/>
+      <c r="A20" s="27" t="s">
+        <v>485</v>
+      </c>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="28"/>
+      <c r="N20" s="28"/>
+      <c r="O20" s="28"/>
+      <c r="P20" s="28"/>
+      <c r="Q20" s="28"/>
+      <c r="R20" s="28"/>
+      <c r="S20" s="28"/>
+      <c r="T20" s="28"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="28"/>
+      <c r="W20" s="28"/>
+      <c r="X20" s="28"/>
+      <c r="Y20" s="28"/>
+      <c r="Z20" s="28"/>
+      <c r="AA20" s="28"/>
+      <c r="AB20" s="28"/>
+      <c r="AC20" s="28"/>
+      <c r="AD20" s="28"/>
+      <c r="AE20" s="28"/>
+      <c r="AF20" s="28"/>
+      <c r="AG20" s="28"/>
+      <c r="AH20" s="28"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="28" t="s">
-        <v>484</v>
-      </c>
-      <c r="B21" s="29">
+      <c r="A21" s="29" t="s">
+        <v>485</v>
+      </c>
+      <c r="B21" s="30">
         <v>2788.48</v>
       </c>
-      <c r="C21" s="29">
+      <c r="C21" s="30">
         <v>1995.8</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>2165.44</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>2623.89</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>4872.02</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>1571.15</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>2390.78</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="30">
         <v>6349.98</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="30">
         <v>4525.3</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="30">
         <v>2715.73</v>
       </c>
-      <c r="L21" s="29">
+      <c r="L21" s="30">
         <v>1965.08</v>
       </c>
-      <c r="M21" s="29">
+      <c r="M21" s="30">
         <v>3084.4</v>
       </c>
-      <c r="N21" s="29">
+      <c r="N21" s="30">
         <v>2528.9</v>
       </c>
-      <c r="O21" s="29">
+      <c r="O21" s="30">
         <v>2521.19</v>
       </c>
-      <c r="P21" s="29">
+      <c r="P21" s="30">
         <v>2779.5</v>
       </c>
-      <c r="Q21" s="29">
+      <c r="Q21" s="30">
         <v>2257.93</v>
       </c>
-      <c r="R21" s="29">
+      <c r="R21" s="30">
         <v>2070.54</v>
       </c>
-      <c r="S21" s="29">
+      <c r="S21" s="30">
         <v>3464.61</v>
       </c>
-      <c r="T21" s="29">
+      <c r="T21" s="30">
         <v>8457.64</v>
       </c>
-      <c r="U21" s="29">
+      <c r="U21" s="30">
         <v>7874.73</v>
       </c>
-      <c r="V21" s="29">
+      <c r="V21" s="30">
         <v>4173.17</v>
       </c>
-      <c r="W21" s="29">
+      <c r="W21" s="30">
         <v>4650.6</v>
       </c>
-      <c r="X21" s="29">
+      <c r="X21" s="30">
         <v>1990.68</v>
       </c>
-      <c r="Y21" s="29">
+      <c r="Y21" s="30">
         <v>3201.16</v>
       </c>
-      <c r="Z21" s="29">
+      <c r="Z21" s="30">
         <v>4026.57</v>
       </c>
-      <c r="AA21" s="29">
+      <c r="AA21" s="30">
         <v>4245.09</v>
       </c>
-      <c r="AB21" s="29">
+      <c r="AB21" s="30">
         <v>6458.15</v>
       </c>
-      <c r="AC21" s="29">
+      <c r="AC21" s="30">
         <v>5527.94</v>
       </c>
-      <c r="AD21" s="29">
+      <c r="AD21" s="30">
         <v>4772.36</v>
       </c>
-      <c r="AE21" s="29">
+      <c r="AE21" s="30">
         <v>2452.65</v>
       </c>
-      <c r="AF21" s="29">
+      <c r="AF21" s="30">
         <v>1918.17</v>
       </c>
-      <c r="AG21" s="29">
+      <c r="AG21" s="30">
         <v>1272.82</v>
       </c>
-      <c r="AH21" s="29">
+      <c r="AH21" s="30">
         <v>840.54</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="28" t="s">
-        <v>485</v>
-      </c>
-      <c r="B22" s="29">
+      <c r="A22" s="29" t="s">
+        <v>486</v>
+      </c>
+      <c r="B22" s="30">
         <v>3094.25</v>
       </c>
-      <c r="C22" s="29">
+      <c r="C22" s="30">
         <v>2818.43</v>
       </c>
-      <c r="D22" s="29">
+      <c r="D22" s="30">
         <v>3109.38</v>
       </c>
-      <c r="E22" s="29">
+      <c r="E22" s="30">
         <v>3615.69</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="30">
         <v>4096.98</v>
       </c>
-      <c r="G22" s="29">
+      <c r="G22" s="30">
         <v>3922.92</v>
       </c>
-      <c r="H22" s="29">
+      <c r="H22" s="30">
         <v>3717.99</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="30">
         <v>3906.72</v>
       </c>
-      <c r="J22" s="29">
+      <c r="J22" s="30">
         <v>3246.74</v>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="30">
         <v>2924.4</v>
       </c>
-      <c r="L22" s="29">
+      <c r="L22" s="30">
         <v>2786.11</v>
       </c>
-      <c r="M22" s="29">
+      <c r="M22" s="30">
         <v>2741.46</v>
       </c>
-      <c r="N22" s="29">
+      <c r="N22" s="30">
         <v>2347.85</v>
       </c>
-      <c r="O22" s="29">
+      <c r="O22" s="30">
         <v>2495.46</v>
       </c>
-      <c r="P22" s="29">
+      <c r="P22" s="30">
         <v>3643.75</v>
       </c>
-      <c r="Q22" s="29">
+      <c r="Q22" s="30">
         <v>4782.27</v>
       </c>
-      <c r="R22" s="29">
+      <c r="R22" s="30">
         <v>5775.07</v>
       </c>
-      <c r="S22" s="29">
+      <c r="S22" s="30">
         <v>5679.03</v>
       </c>
-      <c r="T22" s="29">
+      <c r="T22" s="30">
         <v>5515.08</v>
       </c>
-      <c r="U22" s="29">
+      <c r="U22" s="30">
         <v>4333.62</v>
       </c>
-      <c r="V22" s="29">
+      <c r="V22" s="30">
         <v>3623.53</v>
       </c>
-      <c r="W22" s="29">
+      <c r="W22" s="30">
         <v>3723.84</v>
       </c>
-      <c r="X22" s="29">
+      <c r="X22" s="30">
         <v>3912.34</v>
       </c>
-      <c r="Y22" s="29">
+      <c r="Y22" s="30">
         <v>4332.29</v>
       </c>
-      <c r="Z22" s="29">
+      <c r="Z22" s="30">
         <v>4845.57</v>
       </c>
-      <c r="AA22" s="29">
+      <c r="AA22" s="30">
         <v>4718.15</v>
       </c>
-      <c r="AB22" s="29">
+      <c r="AB22" s="30">
         <v>4227.92</v>
       </c>
-      <c r="AC22" s="29">
+      <c r="AC22" s="30">
         <v>3195.29</v>
       </c>
-      <c r="AD22" s="29">
+      <c r="AD22" s="30">
         <v>2227.8</v>
       </c>
-      <c r="AE22" s="30"/>
-      <c r="AF22" s="30"/>
-      <c r="AG22" s="30"/>
-      <c r="AH22" s="30"/>
+      <c r="AE22" s="31"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="31"/>
+      <c r="AH22" s="31"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="26" t="s">
-        <v>486</v>
-      </c>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="27"/>
-      <c r="X23" s="27"/>
-      <c r="Y23" s="27"/>
-      <c r="Z23" s="27"/>
-      <c r="AA23" s="27"/>
-      <c r="AB23" s="27"/>
-      <c r="AC23" s="27"/>
-      <c r="AD23" s="27"/>
-      <c r="AE23" s="27"/>
-      <c r="AF23" s="27"/>
-      <c r="AG23" s="27"/>
-      <c r="AH23" s="27"/>
+      <c r="A23" s="27" t="s">
+        <v>487</v>
+      </c>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="28"/>
+      <c r="N23" s="28"/>
+      <c r="O23" s="28"/>
+      <c r="P23" s="28"/>
+      <c r="Q23" s="28"/>
+      <c r="R23" s="28"/>
+      <c r="S23" s="28"/>
+      <c r="T23" s="28"/>
+      <c r="U23" s="28"/>
+      <c r="V23" s="28"/>
+      <c r="W23" s="28"/>
+      <c r="X23" s="28"/>
+      <c r="Y23" s="28"/>
+      <c r="Z23" s="28"/>
+      <c r="AA23" s="28"/>
+      <c r="AB23" s="28"/>
+      <c r="AC23" s="28"/>
+      <c r="AD23" s="28"/>
+      <c r="AE23" s="28"/>
+      <c r="AF23" s="28"/>
+      <c r="AG23" s="28"/>
+      <c r="AH23" s="28"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="28" t="s">
-        <v>486</v>
-      </c>
-      <c r="B24" s="29">
+      <c r="A24" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="B24" s="30">
         <v>2996.53</v>
       </c>
-      <c r="C24" s="29">
+      <c r="C24" s="30">
         <v>1944.03</v>
       </c>
-      <c r="D24" s="29">
+      <c r="D24" s="30">
         <v>2195.67</v>
       </c>
-      <c r="E24" s="29">
+      <c r="E24" s="30">
         <v>2766.06</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="30">
         <v>5401.81</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <v>1523.46</v>
       </c>
-      <c r="H24" s="29">
+      <c r="H24" s="30">
         <v>2940.6</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="30">
         <v>7615.06</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="30">
         <v>5672.61</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="30">
         <v>3466.72</v>
       </c>
-      <c r="L24" s="29">
+      <c r="L24" s="30">
         <v>2867.53</v>
       </c>
-      <c r="M24" s="29">
+      <c r="M24" s="30">
         <v>2676.45</v>
       </c>
-      <c r="N24" s="29">
+      <c r="N24" s="30">
         <v>2249.45</v>
       </c>
-      <c r="O24" s="29">
+      <c r="O24" s="30">
         <v>2268.58</v>
       </c>
-      <c r="P24" s="29">
+      <c r="P24" s="30">
         <v>2691.13</v>
       </c>
-      <c r="Q24" s="29">
+      <c r="Q24" s="30">
         <v>2166.36</v>
       </c>
-      <c r="R24" s="29">
+      <c r="R24" s="30">
         <v>1924.6</v>
       </c>
-      <c r="S24" s="29">
+      <c r="S24" s="30">
         <v>3095.41</v>
       </c>
-      <c r="T24" s="29">
+      <c r="T24" s="30">
         <v>8363.49</v>
       </c>
-      <c r="U24" s="29">
+      <c r="U24" s="30">
         <v>8099.62</v>
       </c>
-      <c r="V24" s="29">
+      <c r="V24" s="30">
         <v>4687.9</v>
       </c>
-      <c r="W24" s="29">
+      <c r="W24" s="30">
         <v>4820.24</v>
       </c>
-      <c r="X24" s="29">
+      <c r="X24" s="30">
         <v>2066.76</v>
       </c>
-      <c r="Y24" s="29">
+      <c r="Y24" s="30">
         <v>2917.15</v>
       </c>
-      <c r="Z24" s="29">
+      <c r="Z24" s="30">
         <v>3546.72</v>
       </c>
-      <c r="AA24" s="29">
+      <c r="AA24" s="30">
         <v>3953.92</v>
       </c>
-      <c r="AB24" s="29">
+      <c r="AB24" s="30">
         <v>6367.31</v>
       </c>
-      <c r="AC24" s="29">
+      <c r="AC24" s="30">
         <v>5887.04</v>
       </c>
-      <c r="AD24" s="29">
+      <c r="AD24" s="30">
         <v>4922.75</v>
       </c>
-      <c r="AE24" s="29">
+      <c r="AE24" s="30">
         <v>2556.77</v>
       </c>
-      <c r="AF24" s="29">
+      <c r="AF24" s="30">
         <v>1919.99</v>
       </c>
-      <c r="AG24" s="29">
+      <c r="AG24" s="30">
         <v>1131.37</v>
       </c>
-      <c r="AH24" s="29">
+      <c r="AH24" s="30">
         <v>286.42</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="28" t="s">
-        <v>487</v>
-      </c>
-      <c r="B25" s="29">
+      <c r="A25" s="29" t="s">
+        <v>488</v>
+      </c>
+      <c r="B25" s="30">
         <v>3283.98</v>
       </c>
-      <c r="C25" s="29">
+      <c r="C25" s="30">
         <v>2953.63</v>
       </c>
-      <c r="D25" s="29">
+      <c r="D25" s="30">
         <v>3395.14</v>
       </c>
-      <c r="E25" s="29">
+      <c r="E25" s="30">
         <v>4120.34</v>
       </c>
-      <c r="F25" s="29">
+      <c r="F25" s="30">
         <v>4824.86</v>
       </c>
-      <c r="G25" s="29">
+      <c r="G25" s="30">
         <v>4752.68</v>
       </c>
-      <c r="H25" s="29">
+      <c r="H25" s="30">
         <v>4684.61</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="30">
         <v>4651.39</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="30">
         <v>3664.92</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="30">
         <v>3047.77</v>
       </c>
-      <c r="L25" s="29">
+      <c r="L25" s="30">
         <v>2742.14</v>
       </c>
-      <c r="M25" s="29">
+      <c r="M25" s="30">
         <v>2508.88</v>
       </c>
-      <c r="N25" s="29">
+      <c r="N25" s="30">
         <v>2181.2</v>
       </c>
-      <c r="O25" s="29">
+      <c r="O25" s="30">
         <v>2314.65</v>
       </c>
-      <c r="P25" s="29">
+      <c r="P25" s="30">
         <v>3492.86</v>
       </c>
-      <c r="Q25" s="29">
+      <c r="Q25" s="30">
         <v>4691.29</v>
       </c>
-      <c r="R25" s="29">
+      <c r="R25" s="30">
         <v>5808.95</v>
       </c>
-      <c r="S25" s="29">
+      <c r="S25" s="30">
         <v>5768.03</v>
       </c>
-      <c r="T25" s="29">
+      <c r="T25" s="30">
         <v>5697.48</v>
       </c>
-      <c r="U25" s="29">
+      <c r="U25" s="30">
         <v>4467.45</v>
       </c>
-      <c r="V25" s="29">
+      <c r="V25" s="30">
         <v>3618.09</v>
       </c>
-      <c r="W25" s="29">
+      <c r="W25" s="30">
         <v>3554.12</v>
       </c>
-      <c r="X25" s="29">
+      <c r="X25" s="30">
         <v>3699.64</v>
       </c>
-      <c r="Y25" s="29">
+      <c r="Y25" s="30">
         <v>4181.03</v>
       </c>
-      <c r="Z25" s="29">
+      <c r="Z25" s="30">
         <v>4774.59</v>
       </c>
-      <c r="AA25" s="29">
+      <c r="AA25" s="30">
         <v>4765.23</v>
       </c>
-      <c r="AB25" s="29">
+      <c r="AB25" s="30">
         <v>4333.18</v>
       </c>
-      <c r="AC25" s="29">
+      <c r="AC25" s="30">
         <v>3290.42</v>
       </c>
-      <c r="AD25" s="29">
+      <c r="AD25" s="30">
         <v>2141.14</v>
       </c>
-      <c r="AE25" s="30"/>
-      <c r="AF25" s="30"/>
-      <c r="AG25" s="30"/>
-      <c r="AH25" s="30"/>
+      <c r="AE25" s="31"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="31"/>
+      <c r="AH25" s="31"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="26" t="s">
-        <v>488</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="27"/>
-      <c r="V26" s="27"/>
-      <c r="W26" s="27"/>
-      <c r="X26" s="27"/>
-      <c r="Y26" s="27"/>
-      <c r="Z26" s="27"/>
-      <c r="AA26" s="27"/>
-      <c r="AB26" s="27"/>
-      <c r="AC26" s="27"/>
-      <c r="AD26" s="27"/>
-      <c r="AE26" s="27"/>
-      <c r="AF26" s="27"/>
-      <c r="AG26" s="27"/>
-      <c r="AH26" s="27"/>
+      <c r="A26" s="27" t="s">
+        <v>489</v>
+      </c>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="28"/>
+      <c r="N26" s="28"/>
+      <c r="O26" s="28"/>
+      <c r="P26" s="28"/>
+      <c r="Q26" s="28"/>
+      <c r="R26" s="28"/>
+      <c r="S26" s="28"/>
+      <c r="T26" s="28"/>
+      <c r="U26" s="28"/>
+      <c r="V26" s="28"/>
+      <c r="W26" s="28"/>
+      <c r="X26" s="28"/>
+      <c r="Y26" s="28"/>
+      <c r="Z26" s="28"/>
+      <c r="AA26" s="28"/>
+      <c r="AB26" s="28"/>
+      <c r="AC26" s="28"/>
+      <c r="AD26" s="28"/>
+      <c r="AE26" s="28"/>
+      <c r="AF26" s="28"/>
+      <c r="AG26" s="28"/>
+      <c r="AH26" s="28"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="28" t="s">
-        <v>489</v>
-      </c>
-      <c r="B27" s="31">
+      <c r="A27" s="29" t="s">
+        <v>490</v>
+      </c>
+      <c r="B27" s="32">
         <v>20.34</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <v>15.83</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <v>17.88</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <v>22.53</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>44.0</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <v>15.74</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>30.37</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <v>78.65</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <v>58.59</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <v>35.81</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="32">
         <v>29.62</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="32">
         <v>30.41</v>
       </c>
-      <c r="N27" s="31">
+      <c r="N27" s="32">
         <v>25.56</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="32">
         <v>27.93</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="32">
         <v>33.13</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="32">
         <v>26.67</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="32">
         <v>23.69</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="32">
         <v>61.63</v>
       </c>
-      <c r="T27" s="29">
+      <c r="T27" s="30">
         <v>166.52</v>
       </c>
-      <c r="U27" s="29">
+      <c r="U27" s="30">
         <v>156.5</v>
       </c>
-      <c r="V27" s="31">
+      <c r="V27" s="32">
         <v>90.87</v>
       </c>
-      <c r="W27" s="31">
+      <c r="W27" s="32">
         <v>85.6</v>
       </c>
-      <c r="X27" s="31">
+      <c r="X27" s="32">
         <v>36.83</v>
       </c>
-      <c r="Y27" s="31">
+      <c r="Y27" s="32">
         <v>52.07</v>
       </c>
-      <c r="Z27" s="31">
+      <c r="Z27" s="32">
         <v>63.41</v>
       </c>
-      <c r="AA27" s="31">
+      <c r="AA27" s="32">
         <v>70.69</v>
       </c>
-      <c r="AB27" s="29">
+      <c r="AB27" s="30">
         <v>114.13</v>
       </c>
-      <c r="AC27" s="29">
+      <c r="AC27" s="30">
         <v>105.75</v>
       </c>
-      <c r="AD27" s="31">
+      <c r="AD27" s="32">
         <v>93.29</v>
       </c>
-      <c r="AE27" s="31">
+      <c r="AE27" s="32">
         <v>48.45</v>
       </c>
-      <c r="AF27" s="31">
+      <c r="AF27" s="32">
         <v>36.39</v>
       </c>
-      <c r="AG27" s="31">
+      <c r="AG27" s="32">
         <v>22.02</v>
       </c>
-      <c r="AH27" s="31">
+      <c r="AH27" s="32">
         <v>5.57</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="28" t="s">
-        <v>490</v>
-      </c>
-      <c r="B28" s="31">
+      <c r="A28" s="29" t="s">
+        <v>491</v>
+      </c>
+      <c r="B28" s="32">
         <v>25.94</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>24.76</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>29.95</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>39.02</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>47.48</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <v>49.09</v>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="32">
         <v>48.39</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="32">
         <v>48.69</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="32">
         <v>39.08</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="32">
         <v>33.79</v>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="32">
         <v>31.61</v>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="32">
         <v>29.92</v>
       </c>
-      <c r="N28" s="31">
+      <c r="N28" s="32">
         <v>26.42</v>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="32">
         <v>32.99</v>
       </c>
-      <c r="P28" s="31">
+      <c r="P28" s="32">
         <v>59.7</v>
       </c>
-      <c r="Q28" s="31">
+      <c r="Q28" s="32">
         <v>86.52</v>
       </c>
-      <c r="R28" s="29">
+      <c r="R28" s="30">
         <v>111.09</v>
       </c>
-      <c r="S28" s="29">
+      <c r="S28" s="30">
         <v>111.38</v>
       </c>
-      <c r="T28" s="29">
+      <c r="T28" s="30">
         <v>109.0</v>
       </c>
-      <c r="U28" s="31">
+      <c r="U28" s="32">
         <v>83.44</v>
       </c>
-      <c r="V28" s="31">
+      <c r="V28" s="32">
         <v>65.95</v>
       </c>
-      <c r="W28" s="31">
+      <c r="W28" s="32">
         <v>63.39</v>
       </c>
-      <c r="X28" s="31">
+      <c r="X28" s="32">
         <v>66.16</v>
       </c>
-      <c r="Y28" s="31">
+      <c r="Y28" s="32">
         <v>74.88</v>
       </c>
-      <c r="Z28" s="31">
+      <c r="Z28" s="32">
         <v>86.54</v>
       </c>
-      <c r="AA28" s="31">
+      <c r="AA28" s="32">
         <v>86.98</v>
       </c>
-      <c r="AB28" s="31">
+      <c r="AB28" s="32">
         <v>79.65</v>
       </c>
-      <c r="AC28" s="31">
+      <c r="AC28" s="32">
         <v>61.31</v>
       </c>
-      <c r="AD28" s="31">
+      <c r="AD28" s="32">
         <v>40.72</v>
       </c>
-      <c r="AE28" s="30"/>
-      <c r="AF28" s="30"/>
-      <c r="AG28" s="30"/>
-      <c r="AH28" s="30"/>
+      <c r="AE28" s="31"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="31"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="26" t="s">
-        <v>491</v>
-      </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="27"/>
-      <c r="V29" s="27"/>
-      <c r="W29" s="27"/>
-      <c r="X29" s="27"/>
-      <c r="Y29" s="27"/>
-      <c r="Z29" s="27"/>
-      <c r="AA29" s="27"/>
-      <c r="AB29" s="27"/>
-      <c r="AC29" s="27"/>
-      <c r="AD29" s="27"/>
-      <c r="AE29" s="27"/>
-      <c r="AF29" s="27"/>
-      <c r="AG29" s="27"/>
-      <c r="AH29" s="27"/>
+      <c r="A29" s="27" t="s">
+        <v>492</v>
+      </c>
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28"/>
+      <c r="P29" s="28"/>
+      <c r="Q29" s="28"/>
+      <c r="R29" s="28"/>
+      <c r="S29" s="28"/>
+      <c r="T29" s="28"/>
+      <c r="U29" s="28"/>
+      <c r="V29" s="28"/>
+      <c r="W29" s="28"/>
+      <c r="X29" s="28"/>
+      <c r="Y29" s="28"/>
+      <c r="Z29" s="28"/>
+      <c r="AA29" s="28"/>
+      <c r="AB29" s="28"/>
+      <c r="AC29" s="28"/>
+      <c r="AD29" s="28"/>
+      <c r="AE29" s="28"/>
+      <c r="AF29" s="28"/>
+      <c r="AG29" s="28"/>
+      <c r="AH29" s="28"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="28" t="s">
-        <v>492</v>
-      </c>
-      <c r="B30" s="32">
+      <c r="A30" s="29" t="s">
+        <v>493</v>
+      </c>
+      <c r="B30" s="33">
         <v>0.83</v>
       </c>
-      <c r="C30" s="32">
+      <c r="C30" s="33">
         <v>0.78</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>-1.81</v>
       </c>
-      <c r="E30" s="33">
+      <c r="E30" s="34">
         <v>-8.47</v>
       </c>
-      <c r="F30" s="32">
+      <c r="F30" s="33">
         <v>2.86</v>
       </c>
-      <c r="G30" s="33">
+      <c r="G30" s="34">
         <v>-26.19</v>
       </c>
-      <c r="H30" s="33">
+      <c r="H30" s="34">
         <v>-13.4</v>
       </c>
-      <c r="I30" s="32">
+      <c r="I30" s="33">
         <v>1.36</v>
       </c>
-      <c r="J30" s="32">
+      <c r="J30" s="33">
         <v>2.48</v>
       </c>
-      <c r="K30" s="33">
+      <c r="K30" s="34">
         <v>-7.84</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="34">
         <v>-9.53</v>
       </c>
-      <c r="M30" s="33">
+      <c r="M30" s="34">
         <v>-8.54</v>
       </c>
-      <c r="N30" s="33">
+      <c r="N30" s="34">
         <v>-10.55</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="34">
         <v>-8.59</v>
       </c>
-      <c r="P30" s="33">
+      <c r="P30" s="34">
         <v>-1.16</v>
       </c>
-      <c r="Q30" s="33">
+      <c r="Q30" s="34">
         <v>-3.75</v>
       </c>
-      <c r="R30" s="33">
+      <c r="R30" s="34">
         <v>-19.44</v>
       </c>
-      <c r="S30" s="32">
+      <c r="S30" s="33">
         <v>0.55</v>
       </c>
-      <c r="T30" s="32">
+      <c r="T30" s="33">
         <v>1.88</v>
       </c>
-      <c r="U30" s="32">
+      <c r="U30" s="33">
         <v>0.47</v>
       </c>
-      <c r="V30" s="32">
+      <c r="V30" s="33">
         <v>10.46</v>
       </c>
-      <c r="W30" s="32">
+      <c r="W30" s="33">
         <v>3.85</v>
       </c>
-      <c r="X30" s="32">
+      <c r="X30" s="33">
         <v>18.28</v>
       </c>
-      <c r="Y30" s="32">
+      <c r="Y30" s="33">
         <v>6.68</v>
       </c>
-      <c r="Z30" s="33">
+      <c r="Z30" s="34">
         <v>-4.06</v>
       </c>
-      <c r="AA30" s="33">
+      <c r="AA30" s="34">
         <v>-1.75</v>
       </c>
-      <c r="AB30" s="32">
+      <c r="AB30" s="33">
         <v>1.1</v>
       </c>
-      <c r="AC30" s="32">
+      <c r="AC30" s="33">
         <v>2.99</v>
       </c>
-      <c r="AD30" s="32">
+      <c r="AD30" s="33">
         <v>2.44</v>
       </c>
-      <c r="AE30" s="32">
+      <c r="AE30" s="33">
         <v>4.67</v>
       </c>
-      <c r="AF30" s="32">
+      <c r="AF30" s="33">
         <v>7.24</v>
       </c>
-      <c r="AG30" s="32">
+      <c r="AG30" s="33">
         <v>30.7</v>
       </c>
-      <c r="AH30" s="32">
+      <c r="AH30" s="33">
         <v>29.44</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="28" t="s">
-        <v>493</v>
-      </c>
-      <c r="B31" s="33">
+      <c r="A31" s="29" t="s">
+        <v>494</v>
+      </c>
+      <c r="B31" s="34">
         <v>-0.6</v>
       </c>
-      <c r="C31" s="33">
+      <c r="C31" s="34">
         <v>-4.26</v>
       </c>
-      <c r="D31" s="33">
+      <c r="D31" s="34">
         <v>-7.07</v>
       </c>
-      <c r="E31" s="33">
+      <c r="E31" s="34">
         <v>-3.9</v>
       </c>
-      <c r="F31" s="33">
+      <c r="F31" s="34">
         <v>-1.77</v>
       </c>
-      <c r="G31" s="33">
+      <c r="G31" s="34">
         <v>-3.67</v>
       </c>
-      <c r="H31" s="33">
+      <c r="H31" s="34">
         <v>-3.16</v>
       </c>
-      <c r="I31" s="33">
+      <c r="I31" s="34">
         <v>-2.7</v>
       </c>
-      <c r="J31" s="33">
+      <c r="J31" s="34">
         <v>-5.6</v>
       </c>
-      <c r="K31" s="33">
+      <c r="K31" s="34">
         <v>-8.97</v>
       </c>
-      <c r="L31" s="33">
+      <c r="L31" s="34">
         <v>-7.39</v>
       </c>
-      <c r="M31" s="33">
+      <c r="M31" s="34">
         <v>-6.33</v>
       </c>
-      <c r="N31" s="33">
+      <c r="N31" s="34">
         <v>-7.86</v>
       </c>
-      <c r="O31" s="33">
+      <c r="O31" s="34">
         <v>-4.45</v>
       </c>
-      <c r="P31" s="33">
+      <c r="P31" s="34">
         <v>-0.69</v>
       </c>
-      <c r="Q31" s="33">
+      <c r="Q31" s="34">
         <v>-0.23</v>
       </c>
-      <c r="R31" s="32">
+      <c r="R31" s="33">
         <v>1.92</v>
       </c>
-      <c r="S31" s="32">
+      <c r="S31" s="33">
         <v>3.02</v>
       </c>
-      <c r="T31" s="32">
+      <c r="T31" s="33">
         <v>4.36</v>
       </c>
-      <c r="U31" s="32">
+      <c r="U31" s="33">
         <v>5.62</v>
       </c>
-      <c r="V31" s="32">
+      <c r="V31" s="33">
         <v>6.25</v>
       </c>
-      <c r="W31" s="32">
+      <c r="W31" s="33">
         <v>3.23</v>
       </c>
-      <c r="X31" s="32">
+      <c r="X31" s="33">
         <v>2.38</v>
       </c>
-      <c r="Y31" s="32">
+      <c r="Y31" s="33">
         <v>1.05</v>
       </c>
-      <c r="Z31" s="32">
+      <c r="Z31" s="33">
         <v>0.62</v>
       </c>
-      <c r="AA31" s="32">
+      <c r="AA31" s="33">
         <v>1.79</v>
       </c>
-      <c r="AB31" s="32">
+      <c r="AB31" s="33">
         <v>2.9</v>
       </c>
-      <c r="AC31" s="32">
+      <c r="AC31" s="33">
         <v>5.58</v>
       </c>
-      <c r="AD31" s="32">
+      <c r="AD31" s="33">
         <v>7.55</v>
       </c>
-      <c r="AE31" s="32"/>
-      <c r="AF31" s="32"/>
-      <c r="AG31" s="32"/>
-      <c r="AH31" s="32"/>
+      <c r="AE31" s="33"/>
+      <c r="AF31" s="33"/>
+      <c r="AG31" s="33"/>
+      <c r="AH31" s="33"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="26" t="s">
-        <v>494</v>
-      </c>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-      <c r="W32" s="27"/>
-      <c r="X32" s="27"/>
-      <c r="Y32" s="27"/>
-      <c r="Z32" s="27"/>
-      <c r="AA32" s="27"/>
-      <c r="AB32" s="27"/>
-      <c r="AC32" s="27"/>
-      <c r="AD32" s="27"/>
-      <c r="AE32" s="27"/>
-      <c r="AF32" s="27"/>
-      <c r="AG32" s="27"/>
-      <c r="AH32" s="27"/>
+      <c r="A32" s="27" t="s">
+        <v>495</v>
+      </c>
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28"/>
+      <c r="P32" s="28"/>
+      <c r="Q32" s="28"/>
+      <c r="R32" s="28"/>
+      <c r="S32" s="28"/>
+      <c r="T32" s="28"/>
+      <c r="U32" s="28"/>
+      <c r="V32" s="28"/>
+      <c r="W32" s="28"/>
+      <c r="X32" s="28"/>
+      <c r="Y32" s="28"/>
+      <c r="Z32" s="28"/>
+      <c r="AA32" s="28"/>
+      <c r="AB32" s="28"/>
+      <c r="AC32" s="28"/>
+      <c r="AD32" s="28"/>
+      <c r="AE32" s="28"/>
+      <c r="AF32" s="28"/>
+      <c r="AG32" s="28"/>
+      <c r="AH32" s="28"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="28" t="s">
-        <v>495</v>
-      </c>
-      <c r="B33" s="32">
+      <c r="A33" s="29" t="s">
+        <v>496</v>
+      </c>
+      <c r="B33" s="33">
         <v>0.0</v>
       </c>
-      <c r="C33" s="32">
+      <c r="C33" s="33">
         <v>0.0</v>
       </c>
-      <c r="D33" s="32">
+      <c r="D33" s="33">
         <v>0.0</v>
       </c>
-      <c r="E33" s="32">
+      <c r="E33" s="33">
         <v>0.0</v>
       </c>
-      <c r="F33" s="32">
+      <c r="F33" s="33">
         <v>0.0</v>
       </c>
-      <c r="G33" s="32">
+      <c r="G33" s="33">
         <v>0.0</v>
       </c>
-      <c r="H33" s="32">
+      <c r="H33" s="33">
         <v>0.0</v>
       </c>
-      <c r="I33" s="32">
+      <c r="I33" s="33">
         <v>0.0</v>
       </c>
-      <c r="J33" s="32">
+      <c r="J33" s="33">
         <v>0.0</v>
       </c>
-      <c r="K33" s="32">
+      <c r="K33" s="33">
         <v>0.0</v>
       </c>
-      <c r="L33" s="32">
+      <c r="L33" s="33">
         <v>0.0</v>
       </c>
-      <c r="M33" s="32">
+      <c r="M33" s="33">
         <v>0.0</v>
       </c>
-      <c r="N33" s="32">
+      <c r="N33" s="33">
         <v>0.0</v>
       </c>
-      <c r="O33" s="32">
+      <c r="O33" s="33">
         <v>0.0</v>
       </c>
-      <c r="P33" s="32">
+      <c r="P33" s="33">
         <v>0.0</v>
       </c>
-      <c r="Q33" s="32">
+      <c r="Q33" s="33">
         <v>0.0</v>
       </c>
-      <c r="R33" s="32">
+      <c r="R33" s="33">
         <v>2.38</v>
       </c>
-      <c r="S33" s="32">
+      <c r="S33" s="33">
         <v>5.44</v>
       </c>
-      <c r="T33" s="32">
+      <c r="T33" s="33">
         <v>1.65</v>
       </c>
-      <c r="U33" s="32">
+      <c r="U33" s="33">
         <v>1.26</v>
       </c>
-      <c r="V33" s="32">
+      <c r="V33" s="33">
         <v>1.3</v>
       </c>
-      <c r="W33" s="32">
+      <c r="W33" s="33">
         <v>1.42</v>
       </c>
-      <c r="X33" s="32">
+      <c r="X33" s="33">
         <v>1.58</v>
       </c>
-      <c r="Y33" s="32">
+      <c r="Y33" s="33">
         <v>1.06</v>
       </c>
-      <c r="Z33" s="32">
+      <c r="Z33" s="33">
         <v>1.65</v>
       </c>
-      <c r="AA33" s="32">
+      <c r="AA33" s="33">
         <v>1.29</v>
       </c>
-      <c r="AB33" s="32">
+      <c r="AB33" s="33">
         <v>1.2</v>
       </c>
-      <c r="AC33" s="32">
+      <c r="AC33" s="33">
         <v>0.43</v>
       </c>
-      <c r="AD33" s="32">
+      <c r="AD33" s="33">
         <v>0.29</v>
       </c>
-      <c r="AE33" s="32">
+      <c r="AE33" s="33">
         <v>0.42</v>
       </c>
-      <c r="AF33" s="32">
+      <c r="AF33" s="33">
         <v>0.48</v>
       </c>
-      <c r="AG33" s="32">
+      <c r="AG33" s="33">
         <v>0.0</v>
       </c>
-      <c r="AH33" s="32">
+      <c r="AH33" s="33">
         <v>0.0</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="28" t="s">
-        <v>496</v>
-      </c>
-      <c r="B34" s="32">
+      <c r="A34" s="29" t="s">
+        <v>497</v>
+      </c>
+      <c r="B34" s="33">
         <v>0.0</v>
       </c>
-      <c r="C34" s="32">
+      <c r="C34" s="33">
         <v>0.0</v>
       </c>
-      <c r="D34" s="32">
+      <c r="D34" s="33">
         <v>0.0</v>
       </c>
-      <c r="E34" s="32">
+      <c r="E34" s="33">
         <v>0.0</v>
       </c>
-      <c r="F34" s="32">
+      <c r="F34" s="33">
         <v>0.0</v>
       </c>
-      <c r="G34" s="32">
+      <c r="G34" s="33">
         <v>0.0</v>
       </c>
-      <c r="H34" s="32">
+      <c r="H34" s="33">
         <v>0.0</v>
       </c>
-      <c r="I34" s="32">
+      <c r="I34" s="33">
         <v>0.0</v>
       </c>
-      <c r="J34" s="32">
+      <c r="J34" s="33">
         <v>0.0</v>
       </c>
-      <c r="K34" s="32">
+      <c r="K34" s="33">
         <v>0.0</v>
       </c>
-      <c r="L34" s="32">
+      <c r="L34" s="33">
         <v>0.0</v>
       </c>
-      <c r="M34" s="32">
+      <c r="M34" s="33">
         <v>0.0</v>
       </c>
-      <c r="N34" s="32">
+      <c r="N34" s="33">
         <v>0.37</v>
       </c>
-      <c r="O34" s="32">
+      <c r="O34" s="33">
         <v>2.24</v>
       </c>
-      <c r="P34" s="32">
+      <c r="P34" s="33">
         <v>2.14</v>
       </c>
-      <c r="Q34" s="32">
+      <c r="Q34" s="33">
         <v>1.98</v>
       </c>
-      <c r="R34" s="32">
+      <c r="R34" s="33">
         <v>1.96</v>
       </c>
-      <c r="S34" s="32">
+      <c r="S34" s="33">
         <v>1.87</v>
       </c>
-      <c r="T34" s="32">
+      <c r="T34" s="33">
         <v>1.43</v>
       </c>
-      <c r="U34" s="32">
+      <c r="U34" s="33">
         <v>1.3</v>
       </c>
-      <c r="V34" s="32">
+      <c r="V34" s="33">
         <v>1.39</v>
       </c>
-      <c r="W34" s="32">
+      <c r="W34" s="33">
         <v>1.4</v>
       </c>
-      <c r="X34" s="32">
+      <c r="X34" s="33">
         <v>1.32</v>
       </c>
-      <c r="Y34" s="32">
+      <c r="Y34" s="33">
         <v>1.07</v>
       </c>
-      <c r="Z34" s="32">
+      <c r="Z34" s="33">
         <v>0.91</v>
       </c>
-      <c r="AA34" s="32">
+      <c r="AA34" s="33">
         <v>0.74</v>
       </c>
-      <c r="AB34" s="32">
+      <c r="AB34" s="33">
         <v>0.62</v>
       </c>
-      <c r="AC34" s="32">
+      <c r="AC34" s="33">
         <v>0.36</v>
       </c>
-      <c r="AD34" s="32">
+      <c r="AD34" s="33">
         <v>0.31</v>
       </c>
-      <c r="AE34" s="32"/>
-      <c r="AF34" s="32"/>
-      <c r="AG34" s="32"/>
-      <c r="AH34" s="32"/>
+      <c r="AE34" s="33"/>
+      <c r="AF34" s="33"/>
+      <c r="AG34" s="33"/>
+      <c r="AH34" s="33"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="28" t="s">
-        <v>497</v>
-      </c>
-      <c r="B35" s="32">
+      <c r="A35" s="29" t="s">
+        <v>498</v>
+      </c>
+      <c r="B35" s="33">
         <v>0.0</v>
       </c>
-      <c r="C35" s="32">
+      <c r="C35" s="33">
         <v>0.0</v>
       </c>
-      <c r="D35" s="32">
+      <c r="D35" s="33">
         <v>0.0</v>
       </c>
-      <c r="E35" s="32">
+      <c r="E35" s="33">
         <v>0.0</v>
       </c>
-      <c r="F35" s="32">
+      <c r="F35" s="33">
         <v>0.0</v>
       </c>
-      <c r="G35" s="32">
+      <c r="G35" s="33">
         <v>0.0</v>
       </c>
-      <c r="H35" s="32">
+      <c r="H35" s="33">
         <v>0.0</v>
       </c>
-      <c r="I35" s="32">
+      <c r="I35" s="33">
         <v>0.0</v>
       </c>
-      <c r="J35" s="32">
+      <c r="J35" s="33">
         <v>0.0</v>
       </c>
-      <c r="K35" s="32">
+      <c r="K35" s="33">
         <v>0.0</v>
       </c>
-      <c r="L35" s="32">
+      <c r="L35" s="33">
         <v>0.0</v>
       </c>
-      <c r="M35" s="32">
+      <c r="M35" s="33">
         <v>0.0</v>
       </c>
-      <c r="N35" s="32">
+      <c r="N35" s="33">
         <v>0.0</v>
       </c>
-      <c r="O35" s="32">
+      <c r="O35" s="33">
         <v>0.0</v>
       </c>
-      <c r="P35" s="32">
+      <c r="P35" s="33">
         <v>0.0</v>
       </c>
-      <c r="Q35" s="32">
+      <c r="Q35" s="33">
         <v>0.0</v>
       </c>
-      <c r="R35" s="32">
+      <c r="R35" s="33">
         <v>3.31</v>
       </c>
-      <c r="S35" s="32">
+      <c r="S35" s="33">
         <v>7.56</v>
       </c>
-      <c r="T35" s="32">
+      <c r="T35" s="33">
         <v>2.29</v>
       </c>
-      <c r="U35" s="32">
+      <c r="U35" s="33">
         <v>1.75</v>
       </c>
-      <c r="V35" s="32">
+      <c r="V35" s="33">
         <v>1.8</v>
       </c>
-      <c r="W35" s="32">
+      <c r="W35" s="33">
         <v>1.97</v>
       </c>
-      <c r="X35" s="32">
+      <c r="X35" s="33">
         <v>2.2</v>
       </c>
-      <c r="Y35" s="32">
+      <c r="Y35" s="33">
         <v>1.48</v>
       </c>
-      <c r="Z35" s="32">
+      <c r="Z35" s="33">
         <v>2.21</v>
       </c>
-      <c r="AA35" s="32">
+      <c r="AA35" s="33">
         <v>1.72</v>
       </c>
-      <c r="AB35" s="32">
+      <c r="AB35" s="33">
         <v>1.6</v>
       </c>
-      <c r="AC35" s="32">
+      <c r="AC35" s="33">
         <v>0.57</v>
       </c>
-      <c r="AD35" s="32">
+      <c r="AD35" s="33">
         <v>0.39</v>
       </c>
-      <c r="AE35" s="32">
+      <c r="AE35" s="33">
         <v>0.6</v>
       </c>
-      <c r="AF35" s="32">
+      <c r="AF35" s="33">
         <v>0.68</v>
       </c>
-      <c r="AG35" s="32">
+      <c r="AG35" s="33">
         <v>0.0</v>
       </c>
-      <c r="AH35" s="32">
+      <c r="AH35" s="33">
         <v>0.0</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="28" t="s">
-        <v>498</v>
-      </c>
-      <c r="B36" s="32">
+      <c r="A36" s="29" t="s">
+        <v>499</v>
+      </c>
+      <c r="B36" s="33">
         <v>0.0</v>
       </c>
-      <c r="C36" s="32">
+      <c r="C36" s="33">
         <v>0.0</v>
       </c>
-      <c r="D36" s="32">
+      <c r="D36" s="33">
         <v>0.0</v>
       </c>
-      <c r="E36" s="32">
+      <c r="E36" s="33">
         <v>0.0</v>
       </c>
-      <c r="F36" s="32">
+      <c r="F36" s="33">
         <v>0.0</v>
       </c>
-      <c r="G36" s="32">
+      <c r="G36" s="33">
         <v>0.0</v>
       </c>
-      <c r="H36" s="32">
+      <c r="H36" s="33">
         <v>0.0</v>
       </c>
-      <c r="I36" s="32">
+      <c r="I36" s="33">
         <v>0.0</v>
       </c>
-      <c r="J36" s="32">
+      <c r="J36" s="33">
         <v>0.0</v>
       </c>
-      <c r="K36" s="32">
+      <c r="K36" s="33">
         <v>0.0</v>
       </c>
-      <c r="L36" s="32">
+      <c r="L36" s="33">
         <v>0.0</v>
       </c>
-      <c r="M36" s="32">
+      <c r="M36" s="33">
         <v>0.0</v>
       </c>
-      <c r="N36" s="32">
+      <c r="N36" s="33">
         <v>0.51</v>
       </c>
-      <c r="O36" s="32">
+      <c r="O36" s="33">
         <v>3.11</v>
       </c>
-      <c r="P36" s="32">
+      <c r="P36" s="33">
         <v>2.97</v>
       </c>
-      <c r="Q36" s="32">
+      <c r="Q36" s="33">
         <v>2.75</v>
       </c>
-      <c r="R36" s="32">
+      <c r="R36" s="33">
         <v>2.73</v>
       </c>
-      <c r="S36" s="32">
+      <c r="S36" s="33">
         <v>2.59</v>
       </c>
-      <c r="T36" s="32">
+      <c r="T36" s="33">
         <v>1.99</v>
       </c>
-      <c r="U36" s="32">
+      <c r="U36" s="33">
         <v>1.81</v>
       </c>
-      <c r="V36" s="32">
+      <c r="V36" s="33">
         <v>1.91</v>
       </c>
-      <c r="W36" s="32">
+      <c r="W36" s="33">
         <v>1.9</v>
       </c>
-      <c r="X36" s="32">
+      <c r="X36" s="33">
         <v>1.79</v>
       </c>
-      <c r="Y36" s="32">
+      <c r="Y36" s="33">
         <v>1.44</v>
       </c>
-      <c r="Z36" s="32">
+      <c r="Z36" s="33">
         <v>1.21</v>
       </c>
-      <c r="AA36" s="32">
+      <c r="AA36" s="33">
         <v>0.99</v>
       </c>
-      <c r="AB36" s="32">
+      <c r="AB36" s="33">
         <v>0.84</v>
       </c>
-      <c r="AC36" s="32">
+      <c r="AC36" s="33">
         <v>0.49</v>
       </c>
-      <c r="AD36" s="32">
+      <c r="AD36" s="33">
         <v>0.44</v>
       </c>
-      <c r="AE36" s="32"/>
-      <c r="AF36" s="32"/>
-      <c r="AG36" s="32"/>
-      <c r="AH36" s="32"/>
+      <c r="AE36" s="33"/>
+      <c r="AF36" s="33"/>
+      <c r="AG36" s="33"/>
+      <c r="AH36" s="33"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="26" t="s">
-        <v>499</v>
-      </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="27"/>
-      <c r="V37" s="27"/>
-      <c r="W37" s="27"/>
-      <c r="X37" s="27"/>
-      <c r="Y37" s="27"/>
-      <c r="Z37" s="27"/>
-      <c r="AA37" s="27"/>
-      <c r="AB37" s="27"/>
-      <c r="AC37" s="27"/>
-      <c r="AD37" s="27"/>
-      <c r="AE37" s="27"/>
-      <c r="AF37" s="27"/>
-      <c r="AG37" s="27"/>
-      <c r="AH37" s="27"/>
+      <c r="A37" s="27" t="s">
+        <v>500</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="28"/>
+      <c r="K37" s="28"/>
+      <c r="L37" s="28"/>
+      <c r="M37" s="28"/>
+      <c r="N37" s="28"/>
+      <c r="O37" s="28"/>
+      <c r="P37" s="28"/>
+      <c r="Q37" s="28"/>
+      <c r="R37" s="28"/>
+      <c r="S37" s="28"/>
+      <c r="T37" s="28"/>
+      <c r="U37" s="28"/>
+      <c r="V37" s="28"/>
+      <c r="W37" s="28"/>
+      <c r="X37" s="28"/>
+      <c r="Y37" s="28"/>
+      <c r="Z37" s="28"/>
+      <c r="AA37" s="28"/>
+      <c r="AB37" s="28"/>
+      <c r="AC37" s="28"/>
+      <c r="AD37" s="28"/>
+      <c r="AE37" s="28"/>
+      <c r="AF37" s="28"/>
+      <c r="AG37" s="28"/>
+      <c r="AH37" s="28"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="28" t="s">
-        <v>500</v>
-      </c>
-      <c r="B38" s="31">
+      <c r="A38" s="29" t="s">
+        <v>501</v>
+      </c>
+      <c r="B38" s="32">
         <v>1.65</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>1.32</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>1.41</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>1.81</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>3.42</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <v>1.2</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <v>1.5</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="32">
         <v>3.47</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="32">
         <v>2.8</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="32">
         <v>1.6</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="32">
         <v>1.3</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="32">
         <v>1.53</v>
       </c>
-      <c r="N38" s="31">
+      <c r="N38" s="32">
         <v>1.34</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="32">
         <v>1.37</v>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="32">
         <v>1.68</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="32">
         <v>1.35</v>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="32">
         <v>1.06</v>
       </c>
-      <c r="S38" s="31">
+      <c r="S38" s="32">
         <v>1.98</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="32">
         <v>4.77</v>
       </c>
-      <c r="U38" s="31">
+      <c r="U38" s="32">
         <v>4.64</v>
       </c>
-      <c r="V38" s="31">
+      <c r="V38" s="32">
         <v>2.72</v>
       </c>
-      <c r="W38" s="31">
+      <c r="W38" s="32">
         <v>2.62</v>
       </c>
-      <c r="X38" s="31">
+      <c r="X38" s="32">
         <v>1.29</v>
       </c>
-      <c r="Y38" s="31">
+      <c r="Y38" s="32">
         <v>2.11</v>
       </c>
-      <c r="Z38" s="31">
+      <c r="Z38" s="32">
         <v>2.97</v>
       </c>
-      <c r="AA38" s="31">
+      <c r="AA38" s="32">
         <v>3.42</v>
       </c>
-      <c r="AB38" s="31">
+      <c r="AB38" s="32">
         <v>6.08</v>
       </c>
-      <c r="AC38" s="31">
+      <c r="AC38" s="32">
         <v>4.99</v>
       </c>
-      <c r="AD38" s="31">
+      <c r="AD38" s="32">
         <v>6.4</v>
       </c>
-      <c r="AE38" s="31">
+      <c r="AE38" s="32">
         <v>3.67</v>
       </c>
-      <c r="AF38" s="31">
+      <c r="AF38" s="32">
         <v>5.67</v>
       </c>
-      <c r="AG38" s="31">
+      <c r="AG38" s="32">
         <v>4.3</v>
       </c>
-      <c r="AH38" s="31">
+      <c r="AH38" s="32">
         <v>1.2</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="28" t="s">
-        <v>501</v>
-      </c>
-      <c r="B39" s="31">
+      <c r="A39" s="29" t="s">
+        <v>502</v>
+      </c>
+      <c r="B39" s="32">
         <v>1.97</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <v>1.87</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <v>1.84</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <v>2.37</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <v>2.55</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="32">
         <v>2.22</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="32">
         <v>2.12</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="32">
         <v>2.11</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="32">
         <v>1.68</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="32">
         <v>1.42</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="32">
         <v>1.44</v>
       </c>
-      <c r="M39" s="31">
+      <c r="M39" s="32">
         <v>1.45</v>
       </c>
-      <c r="N39" s="31">
+      <c r="N39" s="32">
         <v>1.36</v>
       </c>
-      <c r="O39" s="31">
+      <c r="O39" s="32">
         <v>1.54</v>
       </c>
-      <c r="P39" s="31">
+      <c r="P39" s="32">
         <v>2.45</v>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="32">
         <v>3.1</v>
       </c>
-      <c r="R39" s="31">
+      <c r="R39" s="32">
         <v>3.24</v>
       </c>
-      <c r="S39" s="31">
+      <c r="S39" s="32">
         <v>3.39</v>
       </c>
-      <c r="T39" s="31">
+      <c r="T39" s="32">
         <v>3.28</v>
       </c>
-      <c r="U39" s="31">
+      <c r="U39" s="32">
         <v>2.76</v>
       </c>
-      <c r="V39" s="31">
+      <c r="V39" s="32">
         <v>2.33</v>
       </c>
-      <c r="W39" s="31">
+      <c r="W39" s="32">
         <v>2.4</v>
       </c>
-      <c r="X39" s="31">
+      <c r="X39" s="32">
         <v>2.92</v>
       </c>
-      <c r="Y39" s="31">
+      <c r="Y39" s="32">
         <v>3.76</v>
       </c>
-      <c r="Z39" s="31">
+      <c r="Z39" s="32">
         <v>4.62</v>
       </c>
-      <c r="AA39" s="31">
+      <c r="AA39" s="32">
         <v>4.89</v>
       </c>
-      <c r="AB39" s="31">
+      <c r="AB39" s="32">
         <v>5.37</v>
       </c>
-      <c r="AC39" s="31">
+      <c r="AC39" s="32">
         <v>5.06</v>
       </c>
-      <c r="AD39" s="31">
+      <c r="AD39" s="32">
         <v>4.68</v>
       </c>
-      <c r="AE39" s="30"/>
-      <c r="AF39" s="30"/>
-      <c r="AG39" s="30"/>
-      <c r="AH39" s="30"/>
+      <c r="AE39" s="31"/>
+      <c r="AF39" s="31"/>
+      <c r="AG39" s="31"/>
+      <c r="AH39" s="31"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="26" t="s">
-        <v>502</v>
-      </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="27"/>
-      <c r="W40" s="27"/>
-      <c r="X40" s="27"/>
-      <c r="Y40" s="27"/>
-      <c r="Z40" s="27"/>
-      <c r="AA40" s="27"/>
-      <c r="AB40" s="27"/>
-      <c r="AC40" s="27"/>
-      <c r="AD40" s="27"/>
-      <c r="AE40" s="27"/>
-      <c r="AF40" s="27"/>
-      <c r="AG40" s="27"/>
-      <c r="AH40" s="27"/>
+      <c r="A40" s="27" t="s">
+        <v>503</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
+      <c r="S40" s="28"/>
+      <c r="T40" s="28"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="28"/>
+      <c r="W40" s="28"/>
+      <c r="X40" s="28"/>
+      <c r="Y40" s="28"/>
+      <c r="Z40" s="28"/>
+      <c r="AA40" s="28"/>
+      <c r="AB40" s="28"/>
+      <c r="AC40" s="28"/>
+      <c r="AD40" s="28"/>
+      <c r="AE40" s="28"/>
+      <c r="AF40" s="28"/>
+      <c r="AG40" s="28"/>
+      <c r="AH40" s="28"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="28" t="s">
-        <v>503</v>
-      </c>
-      <c r="B41" s="31">
+      <c r="A41" s="29" t="s">
+        <v>504</v>
+      </c>
+      <c r="B41" s="32">
         <v>2.71</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <v>2.25</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <v>2.31</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <v>2.6</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <v>4.48</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <v>1.64</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <v>1.78</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="32">
         <v>4.11</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="32">
         <v>3.7</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="32">
         <v>2.18</v>
       </c>
-      <c r="L41" s="31">
+      <c r="L41" s="32">
         <v>1.73</v>
       </c>
-      <c r="M41" s="31">
+      <c r="M41" s="32">
         <v>3.05</v>
       </c>
-      <c r="N41" s="31">
+      <c r="N41" s="32">
         <v>2.42</v>
       </c>
-      <c r="O41" s="31">
+      <c r="O41" s="32">
         <v>2.43</v>
       </c>
-      <c r="P41" s="31">
+      <c r="P41" s="32">
         <v>2.75</v>
       </c>
-      <c r="Q41" s="31">
+      <c r="Q41" s="32">
         <v>1.5</v>
       </c>
-      <c r="R41" s="31">
+      <c r="R41" s="32">
         <v>1.56</v>
       </c>
-      <c r="S41" s="31">
+      <c r="S41" s="32">
         <v>3.09</v>
       </c>
-      <c r="T41" s="31">
+      <c r="T41" s="32">
         <v>3.83</v>
       </c>
-      <c r="U41" s="31">
+      <c r="U41" s="32">
         <v>4.66</v>
       </c>
-      <c r="V41" s="31">
+      <c r="V41" s="32">
         <v>5.19</v>
       </c>
-      <c r="W41" s="31">
+      <c r="W41" s="32">
         <v>3.44</v>
       </c>
-      <c r="X41" s="31">
+      <c r="X41" s="32">
         <v>1.68</v>
       </c>
-      <c r="Y41" s="31">
+      <c r="Y41" s="32">
         <v>2.67</v>
       </c>
-      <c r="Z41" s="31">
+      <c r="Z41" s="32">
         <v>2.9</v>
       </c>
-      <c r="AA41" s="31">
+      <c r="AA41" s="32">
         <v>3.52</v>
       </c>
-      <c r="AB41" s="31">
+      <c r="AB41" s="32">
         <v>5.99</v>
       </c>
-      <c r="AC41" s="31">
+      <c r="AC41" s="32">
         <v>4.9</v>
       </c>
-      <c r="AD41" s="31">
+      <c r="AD41" s="32">
         <v>6.73</v>
       </c>
-      <c r="AE41" s="31">
+      <c r="AE41" s="32">
         <v>3.98</v>
       </c>
-      <c r="AF41" s="31">
+      <c r="AF41" s="32">
         <v>3.6</v>
       </c>
-      <c r="AG41" s="31">
+      <c r="AG41" s="32">
         <v>2.96</v>
       </c>
-      <c r="AH41" s="31">
+      <c r="AH41" s="32">
         <v>0.73</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="28" t="s">
-        <v>504</v>
-      </c>
-      <c r="B42" s="31">
+      <c r="A42" s="29" t="s">
+        <v>505</v>
+      </c>
+      <c r="B42" s="32">
         <v>2.99</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <v>2.74</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="32">
         <v>2.47</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="32">
         <v>2.99</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="32">
         <v>3.2</v>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="32">
         <v>2.83</v>
       </c>
-      <c r="H42" s="31">
+      <c r="H42" s="32">
         <v>2.7</v>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="32">
         <v>2.94</v>
       </c>
-      <c r="J42" s="31">
+      <c r="J42" s="32">
         <v>2.56</v>
       </c>
-      <c r="K42" s="31">
+      <c r="K42" s="32">
         <v>2.29</v>
       </c>
-      <c r="L42" s="31">
+      <c r="L42" s="32">
         <v>2.41</v>
       </c>
-      <c r="M42" s="31">
+      <c r="M42" s="32">
         <v>2.33</v>
       </c>
-      <c r="N42" s="31">
+      <c r="N42" s="32">
         <v>2.06</v>
       </c>
-      <c r="O42" s="31">
+      <c r="O42" s="32">
         <v>2.28</v>
       </c>
-      <c r="P42" s="31">
+      <c r="P42" s="32">
         <v>2.88</v>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q42" s="32">
         <v>3.37</v>
       </c>
-      <c r="R42" s="31">
+      <c r="R42" s="32">
         <v>3.88</v>
       </c>
-      <c r="S42" s="31">
+      <c r="S42" s="32">
         <v>4.03</v>
       </c>
-      <c r="T42" s="31">
+      <c r="T42" s="32">
         <v>3.79</v>
       </c>
-      <c r="U42" s="31">
+      <c r="U42" s="32">
         <v>3.59</v>
       </c>
-      <c r="V42" s="31">
+      <c r="V42" s="32">
         <v>3.1</v>
       </c>
-      <c r="W42" s="31">
+      <c r="W42" s="32">
         <v>2.84</v>
       </c>
-      <c r="X42" s="31">
+      <c r="X42" s="32">
         <v>3.26</v>
       </c>
-      <c r="Y42" s="31">
+      <c r="Y42" s="32">
         <v>3.94</v>
       </c>
-      <c r="Z42" s="31">
+      <c r="Z42" s="32">
         <v>4.63</v>
       </c>
-      <c r="AA42" s="31">
+      <c r="AA42" s="32">
         <v>4.99</v>
       </c>
-      <c r="AB42" s="31">
+      <c r="AB42" s="32">
         <v>5.19</v>
       </c>
-      <c r="AC42" s="31">
+      <c r="AC42" s="32">
         <v>4.7</v>
       </c>
-      <c r="AD42" s="31">
+      <c r="AD42" s="32">
         <v>4.03</v>
       </c>
-      <c r="AE42" s="30"/>
-      <c r="AF42" s="30"/>
-      <c r="AG42" s="30"/>
-      <c r="AH42" s="30"/>
+      <c r="AE42" s="31"/>
+      <c r="AF42" s="31"/>
+      <c r="AG42" s="31"/>
+      <c r="AH42" s="31"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="26" t="s">
-        <v>505</v>
-      </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
-      <c r="T43" s="27"/>
-      <c r="U43" s="27"/>
-      <c r="V43" s="27"/>
-      <c r="W43" s="27"/>
-      <c r="X43" s="27"/>
-      <c r="Y43" s="27"/>
-      <c r="Z43" s="27"/>
-      <c r="AA43" s="27"/>
-      <c r="AB43" s="27"/>
-      <c r="AC43" s="27"/>
-      <c r="AD43" s="27"/>
-      <c r="AE43" s="27"/>
-      <c r="AF43" s="27"/>
-      <c r="AG43" s="27"/>
-      <c r="AH43" s="27"/>
+      <c r="A43" s="27" t="s">
+        <v>506</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+      <c r="K43" s="28"/>
+      <c r="L43" s="28"/>
+      <c r="M43" s="28"/>
+      <c r="N43" s="28"/>
+      <c r="O43" s="28"/>
+      <c r="P43" s="28"/>
+      <c r="Q43" s="28"/>
+      <c r="R43" s="28"/>
+      <c r="S43" s="28"/>
+      <c r="T43" s="28"/>
+      <c r="U43" s="28"/>
+      <c r="V43" s="28"/>
+      <c r="W43" s="28"/>
+      <c r="X43" s="28"/>
+      <c r="Y43" s="28"/>
+      <c r="Z43" s="28"/>
+      <c r="AA43" s="28"/>
+      <c r="AB43" s="28"/>
+      <c r="AC43" s="28"/>
+      <c r="AD43" s="28"/>
+      <c r="AE43" s="28"/>
+      <c r="AF43" s="28"/>
+      <c r="AG43" s="28"/>
+      <c r="AH43" s="28"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="28" t="s">
-        <v>506</v>
-      </c>
-      <c r="B44" s="31">
+      <c r="A44" s="29" t="s">
+        <v>507</v>
+      </c>
+      <c r="B44" s="32">
         <v>0.76</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <v>0.49</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <v>0.5</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <v>0.69</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <v>1.5</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <v>0.49</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <v>0.75</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <v>1.81</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="32">
         <v>1.51</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="32">
         <v>1.05</v>
       </c>
-      <c r="L44" s="31">
+      <c r="L44" s="32">
         <v>1.06</v>
       </c>
-      <c r="M44" s="31">
+      <c r="M44" s="32">
         <v>1.13</v>
       </c>
-      <c r="N44" s="31">
+      <c r="N44" s="32">
         <v>0.74</v>
       </c>
-      <c r="O44" s="31">
+      <c r="O44" s="32">
         <v>0.74</v>
       </c>
-      <c r="P44" s="31">
+      <c r="P44" s="32">
         <v>0.9</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="32">
         <v>0.73</v>
       </c>
-      <c r="R44" s="31">
+      <c r="R44" s="32">
         <v>0.39</v>
       </c>
-      <c r="S44" s="31">
+      <c r="S44" s="32">
         <v>0.74</v>
       </c>
-      <c r="T44" s="31">
+      <c r="T44" s="32">
         <v>1.87</v>
       </c>
-      <c r="U44" s="31">
+      <c r="U44" s="32">
         <v>1.93</v>
       </c>
-      <c r="V44" s="31">
+      <c r="V44" s="32">
         <v>1.26</v>
       </c>
-      <c r="W44" s="31">
+      <c r="W44" s="32">
         <v>1.18</v>
       </c>
-      <c r="X44" s="31">
+      <c r="X44" s="32">
         <v>0.5</v>
       </c>
-      <c r="Y44" s="31">
+      <c r="Y44" s="32">
         <v>0.7</v>
       </c>
-      <c r="Z44" s="31">
+      <c r="Z44" s="32">
         <v>0.89</v>
       </c>
-      <c r="AA44" s="31">
+      <c r="AA44" s="32">
         <v>0.97</v>
       </c>
-      <c r="AB44" s="31">
+      <c r="AB44" s="32">
         <v>1.77</v>
       </c>
-      <c r="AC44" s="31">
+      <c r="AC44" s="32">
         <v>1.86</v>
       </c>
-      <c r="AD44" s="31">
+      <c r="AD44" s="32">
         <v>1.64</v>
       </c>
-      <c r="AE44" s="31">
+      <c r="AE44" s="32">
         <v>0.94</v>
       </c>
-      <c r="AF44" s="31">
+      <c r="AF44" s="32">
         <v>0.71</v>
       </c>
-      <c r="AG44" s="31">
+      <c r="AG44" s="32">
         <v>0.48</v>
       </c>
-      <c r="AH44" s="31">
+      <c r="AH44" s="32">
         <v>0.14</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="28" t="s">
-        <v>507</v>
-      </c>
-      <c r="B45" s="31">
+      <c r="A45" s="29" t="s">
+        <v>508</v>
+      </c>
+      <c r="B45" s="32">
         <v>0.79</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <v>0.73</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <v>0.78</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <v>1.09</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <v>1.25</v>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="32">
         <v>1.17</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="32">
         <v>1.26</v>
       </c>
-      <c r="I45" s="31">
+      <c r="I45" s="32">
         <v>1.35</v>
       </c>
-      <c r="J45" s="31">
+      <c r="J45" s="32">
         <v>1.09</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="32">
         <v>0.92</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L45" s="32">
         <v>0.89</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M45" s="32">
         <v>0.83</v>
       </c>
-      <c r="N45" s="31">
+      <c r="N45" s="32">
         <v>0.67</v>
       </c>
-      <c r="O45" s="31">
+      <c r="O45" s="32">
         <v>0.69</v>
       </c>
-      <c r="P45" s="31">
+      <c r="P45" s="32">
         <v>1.02</v>
       </c>
-      <c r="Q45" s="31">
+      <c r="Q45" s="32">
         <v>1.25</v>
       </c>
-      <c r="R45" s="31">
+      <c r="R45" s="32">
         <v>1.3</v>
       </c>
-      <c r="S45" s="31">
+      <c r="S45" s="32">
         <v>1.41</v>
       </c>
-      <c r="T45" s="31">
+      <c r="T45" s="32">
         <v>1.38</v>
       </c>
-      <c r="U45" s="31">
+      <c r="U45" s="32">
         <v>1.13</v>
       </c>
-      <c r="V45" s="31">
+      <c r="V45" s="32">
         <v>0.9</v>
       </c>
-      <c r="W45" s="31">
+      <c r="W45" s="32">
         <v>0.84</v>
       </c>
-      <c r="X45" s="31">
+      <c r="X45" s="32">
         <v>0.94</v>
       </c>
-      <c r="Y45" s="31">
+      <c r="Y45" s="32">
         <v>1.18</v>
       </c>
-      <c r="Z45" s="31">
+      <c r="Z45" s="32">
         <v>1.38</v>
       </c>
-      <c r="AA45" s="31">
+      <c r="AA45" s="32">
         <v>1.43</v>
       </c>
-      <c r="AB45" s="31">
+      <c r="AB45" s="32">
         <v>1.42</v>
       </c>
-      <c r="AC45" s="31">
+      <c r="AC45" s="32">
         <v>1.17</v>
       </c>
-      <c r="AD45" s="31">
+      <c r="AD45" s="32">
         <v>0.84</v>
       </c>
-      <c r="AE45" s="30"/>
-      <c r="AF45" s="30"/>
-      <c r="AG45" s="30"/>
-      <c r="AH45" s="30"/>
+      <c r="AE45" s="31"/>
+      <c r="AF45" s="31"/>
+      <c r="AG45" s="31"/>
+      <c r="AH45" s="31"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="26" t="s">
-        <v>508</v>
-      </c>
-      <c r="B46" s="27"/>
-      <c r="C46" s="27"/>
-      <c r="D46" s="27"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="27"/>
-      <c r="G46" s="27"/>
-      <c r="H46" s="27"/>
-      <c r="I46" s="27"/>
-      <c r="J46" s="27"/>
-      <c r="K46" s="27"/>
-      <c r="L46" s="27"/>
-      <c r="M46" s="27"/>
-      <c r="N46" s="27"/>
-      <c r="O46" s="27"/>
-      <c r="P46" s="27"/>
-      <c r="Q46" s="27"/>
-      <c r="R46" s="27"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="27"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="27"/>
-      <c r="W46" s="27"/>
-      <c r="X46" s="27"/>
-      <c r="Y46" s="27"/>
-      <c r="Z46" s="27"/>
-      <c r="AA46" s="27"/>
-      <c r="AB46" s="27"/>
-      <c r="AC46" s="27"/>
-      <c r="AD46" s="27"/>
-      <c r="AE46" s="27"/>
-      <c r="AF46" s="27"/>
-      <c r="AG46" s="27"/>
-      <c r="AH46" s="27"/>
+      <c r="A46" s="27" t="s">
+        <v>509</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28"/>
+      <c r="P46" s="28"/>
+      <c r="Q46" s="28"/>
+      <c r="R46" s="28"/>
+      <c r="S46" s="28"/>
+      <c r="T46" s="28"/>
+      <c r="U46" s="28"/>
+      <c r="V46" s="28"/>
+      <c r="W46" s="28"/>
+      <c r="X46" s="28"/>
+      <c r="Y46" s="28"/>
+      <c r="Z46" s="28"/>
+      <c r="AA46" s="28"/>
+      <c r="AB46" s="28"/>
+      <c r="AC46" s="28"/>
+      <c r="AD46" s="28"/>
+      <c r="AE46" s="28"/>
+      <c r="AF46" s="28"/>
+      <c r="AG46" s="28"/>
+      <c r="AH46" s="28"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="28" t="s">
-        <v>509</v>
-      </c>
-      <c r="B47" s="29">
+      <c r="A47" s="29" t="s">
+        <v>510</v>
+      </c>
+      <c r="B47" s="30">
         <v>120.62</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="30">
         <v>127.68</v>
       </c>
-      <c r="D47" s="30"/>
-      <c r="E47" s="30"/>
-      <c r="F47" s="31">
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="32">
         <v>34.92</v>
       </c>
-      <c r="G47" s="30"/>
-      <c r="H47" s="30"/>
-      <c r="I47" s="31">
+      <c r="G47" s="31"/>
+      <c r="H47" s="31"/>
+      <c r="I47" s="32">
         <v>73.61</v>
       </c>
-      <c r="J47" s="31">
+      <c r="J47" s="32">
         <v>40.27</v>
       </c>
-      <c r="K47" s="30"/>
-      <c r="L47" s="30"/>
-      <c r="M47" s="30"/>
-      <c r="N47" s="30"/>
-      <c r="O47" s="30"/>
-      <c r="P47" s="30"/>
-      <c r="Q47" s="30"/>
-      <c r="R47" s="30"/>
-      <c r="S47" s="29">
+      <c r="K47" s="31"/>
+      <c r="L47" s="31"/>
+      <c r="M47" s="31"/>
+      <c r="N47" s="31"/>
+      <c r="O47" s="31"/>
+      <c r="P47" s="31"/>
+      <c r="Q47" s="31"/>
+      <c r="R47" s="31"/>
+      <c r="S47" s="30">
         <v>182.37</v>
       </c>
-      <c r="T47" s="31">
+      <c r="T47" s="32">
         <v>53.32</v>
       </c>
-      <c r="U47" s="29">
+      <c r="U47" s="30">
         <v>214.45</v>
       </c>
-      <c r="V47" s="31">
+      <c r="V47" s="32">
         <v>9.56</v>
       </c>
-      <c r="W47" s="31">
+      <c r="W47" s="32">
         <v>26.0</v>
       </c>
-      <c r="X47" s="31">
+      <c r="X47" s="32">
         <v>5.47</v>
       </c>
-      <c r="Y47" s="31">
+      <c r="Y47" s="32">
         <v>14.97</v>
       </c>
-      <c r="Z47" s="30"/>
-      <c r="AA47" s="30"/>
-      <c r="AB47" s="31">
+      <c r="Z47" s="31"/>
+      <c r="AA47" s="31"/>
+      <c r="AB47" s="32">
         <v>90.54</v>
       </c>
-      <c r="AC47" s="31">
+      <c r="AC47" s="32">
         <v>33.39</v>
       </c>
-      <c r="AD47" s="31">
+      <c r="AD47" s="32">
         <v>40.98</v>
       </c>
-      <c r="AE47" s="31">
+      <c r="AE47" s="32">
         <v>21.42</v>
       </c>
-      <c r="AF47" s="31">
+      <c r="AF47" s="32">
         <v>13.82</v>
       </c>
-      <c r="AG47" s="31">
+      <c r="AG47" s="32">
         <v>3.26</v>
       </c>
-      <c r="AH47" s="31">
+      <c r="AH47" s="32">
         <v>3.4</v>
       </c>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="28" t="s">
-        <v>510</v>
-      </c>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
-      <c r="D48" s="30"/>
-      <c r="E48" s="30"/>
-      <c r="F48" s="30"/>
-      <c r="G48" s="30"/>
-      <c r="H48" s="30"/>
-      <c r="I48" s="30"/>
-      <c r="J48" s="30"/>
-      <c r="K48" s="30"/>
-      <c r="L48" s="30"/>
-      <c r="M48" s="30"/>
-      <c r="N48" s="30"/>
-      <c r="O48" s="30"/>
-      <c r="P48" s="30"/>
-      <c r="Q48" s="30"/>
-      <c r="R48" s="31">
+      <c r="A48" s="29" t="s">
+        <v>511</v>
+      </c>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="31"/>
+      <c r="M48" s="31"/>
+      <c r="N48" s="31"/>
+      <c r="O48" s="31"/>
+      <c r="P48" s="31"/>
+      <c r="Q48" s="31"/>
+      <c r="R48" s="32">
         <v>52.11</v>
       </c>
-      <c r="S48" s="31">
+      <c r="S48" s="32">
         <v>33.16</v>
       </c>
-      <c r="T48" s="31">
+      <c r="T48" s="32">
         <v>22.92</v>
       </c>
-      <c r="U48" s="31">
+      <c r="U48" s="32">
         <v>17.8</v>
       </c>
-      <c r="V48" s="31">
+      <c r="V48" s="32">
         <v>16.01</v>
       </c>
-      <c r="W48" s="31">
+      <c r="W48" s="32">
         <v>30.96</v>
       </c>
-      <c r="X48" s="31">
+      <c r="X48" s="32">
         <v>42.06</v>
       </c>
-      <c r="Y48" s="31">
+      <c r="Y48" s="32">
         <v>95.08</v>
       </c>
-      <c r="Z48" s="29">
+      <c r="Z48" s="30">
         <v>160.29</v>
       </c>
-      <c r="AA48" s="31">
+      <c r="AA48" s="32">
         <v>55.82</v>
       </c>
-      <c r="AB48" s="31">
+      <c r="AB48" s="32">
         <v>34.44</v>
       </c>
-      <c r="AC48" s="31">
+      <c r="AC48" s="32">
         <v>17.92</v>
       </c>
-      <c r="AD48" s="31">
+      <c r="AD48" s="32">
         <v>13.24</v>
       </c>
-      <c r="AE48" s="30"/>
-      <c r="AF48" s="30"/>
-      <c r="AG48" s="30"/>
-      <c r="AH48" s="30"/>
+      <c r="AE48" s="31"/>
+      <c r="AF48" s="31"/>
+      <c r="AG48" s="31"/>
+      <c r="AH48" s="31"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="26" t="s">
-        <v>511</v>
-      </c>
-      <c r="B49" s="27"/>
-      <c r="C49" s="27"/>
-      <c r="D49" s="27"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
-      <c r="G49" s="27"/>
-      <c r="H49" s="27"/>
-      <c r="I49" s="27"/>
-      <c r="J49" s="27"/>
-      <c r="K49" s="27"/>
-      <c r="L49" s="27"/>
-      <c r="M49" s="27"/>
-      <c r="N49" s="27"/>
-      <c r="O49" s="27"/>
-      <c r="P49" s="27"/>
-      <c r="Q49" s="27"/>
-      <c r="R49" s="27"/>
-      <c r="S49" s="27"/>
-      <c r="T49" s="27"/>
-      <c r="U49" s="27"/>
-      <c r="V49" s="27"/>
-      <c r="W49" s="27"/>
-      <c r="X49" s="27"/>
-      <c r="Y49" s="27"/>
-      <c r="Z49" s="27"/>
-      <c r="AA49" s="27"/>
-      <c r="AB49" s="27"/>
-      <c r="AC49" s="27"/>
-      <c r="AD49" s="27"/>
-      <c r="AE49" s="27"/>
-      <c r="AF49" s="27"/>
-      <c r="AG49" s="27"/>
-      <c r="AH49" s="27"/>
+      <c r="A49" s="27" t="s">
+        <v>512</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28"/>
+      <c r="H49" s="28"/>
+      <c r="I49" s="28"/>
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28"/>
+      <c r="P49" s="28"/>
+      <c r="Q49" s="28"/>
+      <c r="R49" s="28"/>
+      <c r="S49" s="28"/>
+      <c r="T49" s="28"/>
+      <c r="U49" s="28"/>
+      <c r="V49" s="28"/>
+      <c r="W49" s="28"/>
+      <c r="X49" s="28"/>
+      <c r="Y49" s="28"/>
+      <c r="Z49" s="28"/>
+      <c r="AA49" s="28"/>
+      <c r="AB49" s="28"/>
+      <c r="AC49" s="28"/>
+      <c r="AD49" s="28"/>
+      <c r="AE49" s="28"/>
+      <c r="AF49" s="28"/>
+      <c r="AG49" s="28"/>
+      <c r="AH49" s="28"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="28" t="s">
-        <v>512</v>
-      </c>
-      <c r="B50" s="31">
+      <c r="A50" s="29" t="s">
+        <v>513</v>
+      </c>
+      <c r="B50" s="32">
         <v>9.15</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="32">
         <v>5.88</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="32">
         <v>17.04</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="32">
         <v>11.29</v>
       </c>
-      <c r="F50" s="31">
+      <c r="F50" s="32">
         <v>24.97</v>
       </c>
-      <c r="G50" s="30"/>
-      <c r="H50" s="31">
+      <c r="G50" s="31"/>
+      <c r="H50" s="32">
         <v>10.68</v>
       </c>
-      <c r="I50" s="31">
+      <c r="I50" s="32">
         <v>16.75</v>
       </c>
-      <c r="J50" s="31">
+      <c r="J50" s="32">
         <v>25.62</v>
       </c>
-      <c r="K50" s="31">
+      <c r="K50" s="32">
         <v>87.22</v>
       </c>
-      <c r="L50" s="30"/>
-      <c r="M50" s="31">
+      <c r="L50" s="31"/>
+      <c r="M50" s="32">
         <v>20.85</v>
       </c>
-      <c r="N50" s="31">
+      <c r="N50" s="32">
         <v>12.13</v>
       </c>
-      <c r="O50" s="31">
+      <c r="O50" s="32">
         <v>3.94</v>
       </c>
-      <c r="P50" s="31">
+      <c r="P50" s="32">
         <v>8.16</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="32">
         <v>6.69</v>
       </c>
-      <c r="R50" s="30"/>
-      <c r="S50" s="31">
+      <c r="R50" s="31"/>
+      <c r="S50" s="32">
         <v>8.52</v>
       </c>
-      <c r="T50" s="31">
+      <c r="T50" s="32">
         <v>13.14</v>
       </c>
-      <c r="U50" s="31">
+      <c r="U50" s="32">
         <v>21.06</v>
       </c>
-      <c r="V50" s="31">
+      <c r="V50" s="32">
         <v>11.96</v>
       </c>
-      <c r="W50" s="31">
+      <c r="W50" s="32">
         <v>9.24</v>
       </c>
-      <c r="X50" s="31">
+      <c r="X50" s="32">
         <v>5.58</v>
       </c>
-      <c r="Y50" s="31">
+      <c r="Y50" s="32">
         <v>9.73</v>
       </c>
-      <c r="Z50" s="31">
+      <c r="Z50" s="32">
         <v>14.15</v>
       </c>
-      <c r="AA50" s="31">
+      <c r="AA50" s="32">
         <v>11.7</v>
       </c>
-      <c r="AB50" s="31">
+      <c r="AB50" s="32">
         <v>26.47</v>
       </c>
-      <c r="AC50" s="31">
+      <c r="AC50" s="32">
         <v>16.77</v>
       </c>
-      <c r="AD50" s="31">
+      <c r="AD50" s="32">
         <v>21.29</v>
       </c>
-      <c r="AE50" s="31">
+      <c r="AE50" s="32">
         <v>8.31</v>
       </c>
-      <c r="AF50" s="31">
+      <c r="AF50" s="32">
         <v>6.05</v>
       </c>
-      <c r="AG50" s="31">
+      <c r="AG50" s="32">
         <v>4.52</v>
       </c>
-      <c r="AH50" s="31">
+      <c r="AH50" s="32">
         <v>2.18</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
-        <v>513</v>
-      </c>
-      <c r="B51" s="31">
+      <c r="A51" s="29" t="s">
+        <v>514</v>
+      </c>
+      <c r="B51" s="32">
         <v>12.62</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="32">
         <v>75.19</v>
       </c>
-      <c r="D51" s="31">
+      <c r="D51" s="32">
         <v>63.36</v>
       </c>
-      <c r="E51" s="31">
+      <c r="E51" s="32">
         <v>32.16</v>
       </c>
-      <c r="F51" s="31">
+      <c r="F51" s="32">
         <v>36.12</v>
       </c>
-      <c r="G51" s="31">
+      <c r="G51" s="32">
         <v>44.21</v>
       </c>
-      <c r="H51" s="31">
+      <c r="H51" s="32">
         <v>34.38</v>
       </c>
-      <c r="I51" s="31">
+      <c r="I51" s="32">
         <v>41.73</v>
       </c>
-      <c r="J51" s="31">
+      <c r="J51" s="32">
         <v>52.04</v>
       </c>
-      <c r="K51" s="31">
+      <c r="K51" s="32">
         <v>16.6</v>
       </c>
-      <c r="L51" s="31">
+      <c r="L51" s="32">
         <v>11.8</v>
       </c>
-      <c r="M51" s="31">
+      <c r="M51" s="32">
         <v>7.62</v>
       </c>
-      <c r="N51" s="30"/>
-      <c r="O51" s="30"/>
-      <c r="P51" s="30"/>
-      <c r="Q51" s="30"/>
-      <c r="R51" s="29">
+      <c r="N51" s="31"/>
+      <c r="O51" s="31"/>
+      <c r="P51" s="31"/>
+      <c r="Q51" s="31"/>
+      <c r="R51" s="30">
         <v>480.85</v>
       </c>
-      <c r="S51" s="31">
+      <c r="S51" s="32">
         <v>12.74</v>
       </c>
-      <c r="T51" s="31">
+      <c r="T51" s="32">
         <v>12.35</v>
       </c>
-      <c r="U51" s="31">
+      <c r="U51" s="32">
         <v>11.67</v>
       </c>
-      <c r="V51" s="31">
+      <c r="V51" s="32">
         <v>9.87</v>
       </c>
-      <c r="W51" s="31">
+      <c r="W51" s="32">
         <v>9.7</v>
       </c>
-      <c r="X51" s="31">
+      <c r="X51" s="32">
         <v>12.46</v>
       </c>
-      <c r="Y51" s="31">
+      <c r="Y51" s="32">
         <v>15.21</v>
       </c>
-      <c r="Z51" s="31">
+      <c r="Z51" s="32">
         <v>17.51</v>
       </c>
-      <c r="AA51" s="31">
+      <c r="AA51" s="32">
         <v>16.1</v>
       </c>
-      <c r="AB51" s="31">
+      <c r="AB51" s="32">
         <v>14.89</v>
       </c>
-      <c r="AC51" s="31">
+      <c r="AC51" s="32">
         <v>11.21</v>
       </c>
-      <c r="AD51" s="31">
+      <c r="AD51" s="32">
         <v>8.74</v>
       </c>
-      <c r="AE51" s="30"/>
-      <c r="AF51" s="30"/>
-      <c r="AG51" s="30"/>
-      <c r="AH51" s="30"/>
+      <c r="AE51" s="31"/>
+      <c r="AF51" s="31"/>
+      <c r="AG51" s="31"/>
+      <c r="AH51" s="31"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="26" t="s">
-        <v>514</v>
-      </c>
-      <c r="B52" s="27"/>
-      <c r="C52" s="27"/>
-      <c r="D52" s="27"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="27"/>
-      <c r="G52" s="27"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="27"/>
-      <c r="J52" s="27"/>
-      <c r="K52" s="27"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="27"/>
-      <c r="N52" s="27"/>
-      <c r="O52" s="27"/>
-      <c r="P52" s="27"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="27"/>
-      <c r="S52" s="27"/>
-      <c r="T52" s="27"/>
-      <c r="U52" s="27"/>
-      <c r="V52" s="27"/>
-      <c r="W52" s="27"/>
-      <c r="X52" s="27"/>
-      <c r="Y52" s="27"/>
-      <c r="Z52" s="27"/>
-      <c r="AA52" s="27"/>
-      <c r="AB52" s="27"/>
-      <c r="AC52" s="27"/>
-      <c r="AD52" s="27"/>
-      <c r="AE52" s="27"/>
-      <c r="AF52" s="27"/>
-      <c r="AG52" s="27"/>
-      <c r="AH52" s="27"/>
+      <c r="A52" s="27" t="s">
+        <v>515</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="28"/>
+      <c r="S52" s="28"/>
+      <c r="T52" s="28"/>
+      <c r="U52" s="28"/>
+      <c r="V52" s="28"/>
+      <c r="W52" s="28"/>
+      <c r="X52" s="28"/>
+      <c r="Y52" s="28"/>
+      <c r="Z52" s="28"/>
+      <c r="AA52" s="28"/>
+      <c r="AB52" s="28"/>
+      <c r="AC52" s="28"/>
+      <c r="AD52" s="28"/>
+      <c r="AE52" s="28"/>
+      <c r="AF52" s="28"/>
+      <c r="AG52" s="28"/>
+      <c r="AH52" s="28"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="28" t="s">
-        <v>515</v>
-      </c>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
-      <c r="D53" s="30"/>
-      <c r="E53" s="30"/>
-      <c r="F53" s="30"/>
-      <c r="G53" s="30"/>
-      <c r="H53" s="29">
+      <c r="A53" s="29" t="s">
+        <v>516</v>
+      </c>
+      <c r="B53" s="31"/>
+      <c r="C53" s="31"/>
+      <c r="D53" s="31"/>
+      <c r="E53" s="31"/>
+      <c r="F53" s="31"/>
+      <c r="G53" s="31"/>
+      <c r="H53" s="30">
         <v>111.91</v>
       </c>
-      <c r="I53" s="31">
+      <c r="I53" s="32">
         <v>73.61</v>
       </c>
-      <c r="J53" s="30"/>
-      <c r="K53" s="30"/>
-      <c r="L53" s="30"/>
-      <c r="M53" s="30"/>
-      <c r="N53" s="30"/>
-      <c r="O53" s="31">
+      <c r="J53" s="31"/>
+      <c r="K53" s="31"/>
+      <c r="L53" s="31"/>
+      <c r="M53" s="31"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="32">
         <v>30.43</v>
       </c>
-      <c r="P53" s="31">
+      <c r="P53" s="32">
         <v>96.21</v>
       </c>
-      <c r="Q53" s="31">
+      <c r="Q53" s="32">
         <v>92.85</v>
       </c>
-      <c r="R53" s="30"/>
-      <c r="S53" s="31">
+      <c r="R53" s="31"/>
+      <c r="S53" s="32">
         <v>28.74</v>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="32">
         <v>10.9</v>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="32">
         <v>13.6</v>
       </c>
-      <c r="V53" s="31">
+      <c r="V53" s="32">
         <v>8.71</v>
       </c>
-      <c r="W53" s="31">
+      <c r="W53" s="32">
         <v>16.08</v>
       </c>
-      <c r="X53" s="31">
+      <c r="X53" s="32">
         <v>10.5</v>
       </c>
-      <c r="Y53" s="31">
+      <c r="Y53" s="32">
         <v>19.98</v>
       </c>
-      <c r="Z53" s="31">
+      <c r="Z53" s="32">
         <v>22.14</v>
       </c>
-      <c r="AA53" s="31">
+      <c r="AA53" s="32">
         <v>14.87</v>
       </c>
-      <c r="AB53" s="31">
+      <c r="AB53" s="32">
         <v>31.34</v>
       </c>
-      <c r="AC53" s="31">
+      <c r="AC53" s="32">
         <v>18.85</v>
       </c>
-      <c r="AD53" s="31">
+      <c r="AD53" s="32">
         <v>28.92</v>
       </c>
-      <c r="AE53" s="31">
+      <c r="AE53" s="32">
         <v>17.77</v>
       </c>
-      <c r="AF53" s="31">
+      <c r="AF53" s="32">
         <v>13.77</v>
       </c>
-      <c r="AG53" s="31">
+      <c r="AG53" s="32">
         <v>11.56</v>
       </c>
-      <c r="AH53" s="31">
+      <c r="AH53" s="32">
         <v>24.34</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
-        <v>516</v>
-      </c>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
-      <c r="D54" s="30"/>
-      <c r="E54" s="30"/>
-      <c r="F54" s="30"/>
-      <c r="G54" s="30"/>
-      <c r="H54" s="30"/>
-      <c r="I54" s="30"/>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
-      <c r="L54" s="30"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="30"/>
-      <c r="O54" s="30"/>
-      <c r="P54" s="30"/>
-      <c r="Q54" s="30"/>
-      <c r="R54" s="30"/>
-      <c r="S54" s="31">
+      <c r="A54" s="29" t="s">
+        <v>517</v>
+      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="31"/>
+      <c r="K54" s="31"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="31"/>
+      <c r="P54" s="31"/>
+      <c r="Q54" s="31"/>
+      <c r="R54" s="31"/>
+      <c r="S54" s="32">
         <v>12.56</v>
       </c>
-      <c r="T54" s="31">
+      <c r="T54" s="32">
         <v>11.65</v>
       </c>
-      <c r="U54" s="31">
+      <c r="U54" s="32">
         <v>12.66</v>
       </c>
-      <c r="V54" s="31">
+      <c r="V54" s="32">
         <v>13.32</v>
       </c>
-      <c r="W54" s="31">
+      <c r="W54" s="32">
         <v>16.24</v>
       </c>
-      <c r="X54" s="31">
+      <c r="X54" s="32">
         <v>19.35</v>
       </c>
-      <c r="Y54" s="31">
+      <c r="Y54" s="32">
         <v>20.85</v>
       </c>
-      <c r="Z54" s="31">
+      <c r="Z54" s="32">
         <v>22.28</v>
       </c>
-      <c r="AA54" s="31">
+      <c r="AA54" s="32">
         <v>21.68</v>
       </c>
-      <c r="AB54" s="31">
+      <c r="AB54" s="32">
         <v>22.35</v>
       </c>
-      <c r="AC54" s="31">
+      <c r="AC54" s="32">
         <v>19.03</v>
       </c>
-      <c r="AD54" s="31">
+      <c r="AD54" s="32">
         <v>19.24</v>
       </c>
-      <c r="AE54" s="30"/>
-      <c r="AF54" s="30"/>
-      <c r="AG54" s="30"/>
-      <c r="AH54" s="30"/>
+      <c r="AE54" s="31"/>
+      <c r="AF54" s="31"/>
+      <c r="AG54" s="31"/>
+      <c r="AH54" s="31"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="26" t="s">
-        <v>517</v>
-      </c>
-      <c r="B55" s="27"/>
-      <c r="C55" s="27"/>
-      <c r="D55" s="27"/>
-      <c r="E55" s="27"/>
-      <c r="F55" s="27"/>
-      <c r="G55" s="27"/>
-      <c r="H55" s="27"/>
-      <c r="I55" s="27"/>
-      <c r="J55" s="27"/>
-      <c r="K55" s="27"/>
-      <c r="L55" s="27"/>
-      <c r="M55" s="27"/>
-      <c r="N55" s="27"/>
-      <c r="O55" s="27"/>
-      <c r="P55" s="27"/>
-      <c r="Q55" s="27"/>
-      <c r="R55" s="27"/>
-      <c r="S55" s="27"/>
-      <c r="T55" s="27"/>
-      <c r="U55" s="27"/>
-      <c r="V55" s="27"/>
-      <c r="W55" s="27"/>
-      <c r="X55" s="27"/>
-      <c r="Y55" s="27"/>
-      <c r="Z55" s="27"/>
-      <c r="AA55" s="27"/>
-      <c r="AB55" s="27"/>
-      <c r="AC55" s="27"/>
-      <c r="AD55" s="27"/>
-      <c r="AE55" s="27"/>
-      <c r="AF55" s="27"/>
-      <c r="AG55" s="27"/>
-      <c r="AH55" s="27"/>
+      <c r="A55" s="27" t="s">
+        <v>518</v>
+      </c>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28"/>
+      <c r="E55" s="28"/>
+      <c r="F55" s="28"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28"/>
+      <c r="I55" s="28"/>
+      <c r="J55" s="28"/>
+      <c r="K55" s="28"/>
+      <c r="L55" s="28"/>
+      <c r="M55" s="28"/>
+      <c r="N55" s="28"/>
+      <c r="O55" s="28"/>
+      <c r="P55" s="28"/>
+      <c r="Q55" s="28"/>
+      <c r="R55" s="28"/>
+      <c r="S55" s="28"/>
+      <c r="T55" s="28"/>
+      <c r="U55" s="28"/>
+      <c r="V55" s="28"/>
+      <c r="W55" s="28"/>
+      <c r="X55" s="28"/>
+      <c r="Y55" s="28"/>
+      <c r="Z55" s="28"/>
+      <c r="AA55" s="28"/>
+      <c r="AB55" s="28"/>
+      <c r="AC55" s="28"/>
+      <c r="AD55" s="28"/>
+      <c r="AE55" s="28"/>
+      <c r="AF55" s="28"/>
+      <c r="AG55" s="28"/>
+      <c r="AH55" s="28"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="28" t="s">
-        <v>518</v>
-      </c>
-      <c r="B56" s="30"/>
-      <c r="C56" s="29">
+      <c r="A56" s="29" t="s">
+        <v>519</v>
+      </c>
+      <c r="B56" s="31"/>
+      <c r="C56" s="30">
         <v>127.69</v>
       </c>
-      <c r="D56" s="30"/>
-      <c r="E56" s="30"/>
-      <c r="F56" s="29">
+      <c r="D56" s="31"/>
+      <c r="E56" s="31"/>
+      <c r="F56" s="30">
         <v>657.66</v>
       </c>
-      <c r="G56" s="30"/>
-      <c r="H56" s="31">
+      <c r="G56" s="31"/>
+      <c r="H56" s="32">
         <v>73.32</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="32">
         <v>73.61</v>
       </c>
-      <c r="J56" s="30"/>
-      <c r="K56" s="30"/>
-      <c r="L56" s="30"/>
-      <c r="M56" s="30"/>
-      <c r="N56" s="30"/>
-      <c r="O56" s="31">
+      <c r="J56" s="31"/>
+      <c r="K56" s="31"/>
+      <c r="L56" s="31"/>
+      <c r="M56" s="31"/>
+      <c r="N56" s="31"/>
+      <c r="O56" s="32">
         <v>30.43</v>
       </c>
-      <c r="P56" s="31">
+      <c r="P56" s="32">
         <v>96.21</v>
       </c>
-      <c r="Q56" s="31">
+      <c r="Q56" s="32">
         <v>36.47</v>
       </c>
-      <c r="R56" s="30"/>
-      <c r="S56" s="31">
+      <c r="R56" s="31"/>
+      <c r="S56" s="32">
         <v>64.85</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="32">
         <v>22.22</v>
       </c>
-      <c r="U56" s="31">
+      <c r="U56" s="32">
         <v>53.4</v>
       </c>
-      <c r="V56" s="31">
+      <c r="V56" s="32">
         <v>31.34</v>
       </c>
-      <c r="W56" s="31">
+      <c r="W56" s="32">
         <v>24.43</v>
       </c>
-      <c r="X56" s="31">
+      <c r="X56" s="32">
         <v>21.57</v>
       </c>
-      <c r="Y56" s="31">
+      <c r="Y56" s="32">
         <v>57.49</v>
       </c>
-      <c r="Z56" s="31">
+      <c r="Z56" s="32">
         <v>45.51</v>
       </c>
-      <c r="AA56" s="31">
+      <c r="AA56" s="32">
         <v>24.49</v>
       </c>
-      <c r="AB56" s="31">
+      <c r="AB56" s="32">
         <v>38.0</v>
       </c>
-      <c r="AC56" s="31">
+      <c r="AC56" s="32">
         <v>30.61</v>
       </c>
-      <c r="AD56" s="31">
+      <c r="AD56" s="32">
         <v>75.09</v>
       </c>
-      <c r="AE56" s="31">
+      <c r="AE56" s="32">
         <v>17.77</v>
       </c>
-      <c r="AF56" s="31">
+      <c r="AF56" s="32">
         <v>13.77</v>
       </c>
-      <c r="AG56" s="31">
+      <c r="AG56" s="32">
         <v>10.9</v>
       </c>
-      <c r="AH56" s="31">
+      <c r="AH56" s="32">
         <v>18.37</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
-        <v>519</v>
-      </c>
-      <c r="B57" s="31">
+      <c r="A57" s="29" t="s">
+        <v>520</v>
+      </c>
+      <c r="B57" s="32">
         <v>1.97</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="32">
         <v>1.87</v>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="32">
         <v>1.84</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="32">
         <v>2.37</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="32">
         <v>2.55</v>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="32">
         <v>2.22</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H57" s="32">
         <v>2.12</v>
       </c>
-      <c r="I57" s="31">
+      <c r="I57" s="32">
         <v>2.11</v>
       </c>
-      <c r="J57" s="31">
+      <c r="J57" s="32">
         <v>1.68</v>
       </c>
-      <c r="K57" s="31">
+      <c r="K57" s="32">
         <v>1.42</v>
       </c>
-      <c r="L57" s="31">
+      <c r="L57" s="32">
         <v>1.44</v>
       </c>
-      <c r="M57" s="31">
+      <c r="M57" s="32">
         <v>1.45</v>
       </c>
-      <c r="N57" s="31">
+      <c r="N57" s="32">
         <v>1.36</v>
       </c>
-      <c r="O57" s="31">
+      <c r="O57" s="32">
         <v>1.56</v>
       </c>
-      <c r="P57" s="31">
+      <c r="P57" s="32">
         <v>2.45</v>
       </c>
-      <c r="Q57" s="31">
+      <c r="Q57" s="32">
         <v>3.06</v>
       </c>
-      <c r="R57" s="31">
+      <c r="R57" s="32">
         <v>3.17</v>
       </c>
-      <c r="S57" s="31">
+      <c r="S57" s="32">
         <v>3.29</v>
       </c>
-      <c r="T57" s="31">
+      <c r="T57" s="32">
         <v>3.13</v>
       </c>
-      <c r="U57" s="31">
+      <c r="U57" s="32">
         <v>2.63</v>
       </c>
-      <c r="V57" s="31">
+      <c r="V57" s="32">
         <v>2.22</v>
       </c>
-      <c r="W57" s="31">
+      <c r="W57" s="32">
         <v>2.29</v>
       </c>
-      <c r="X57" s="31">
+      <c r="X57" s="32">
         <v>2.78</v>
       </c>
-      <c r="Y57" s="31">
+      <c r="Y57" s="32">
         <v>3.59</v>
       </c>
-      <c r="Z57" s="31">
+      <c r="Z57" s="32">
         <v>4.41</v>
       </c>
-      <c r="AA57" s="31">
+      <c r="AA57" s="32">
         <v>4.67</v>
       </c>
-      <c r="AB57" s="31">
+      <c r="AB57" s="32">
         <v>4.8</v>
       </c>
-      <c r="AC57" s="31">
+      <c r="AC57" s="32">
         <v>4.18</v>
       </c>
-      <c r="AD57" s="31">
+      <c r="AD57" s="32">
         <v>3.43</v>
       </c>
-      <c r="AE57" s="30"/>
-      <c r="AF57" s="30"/>
-      <c r="AG57" s="30"/>
-      <c r="AH57" s="30"/>
+      <c r="AE57" s="31"/>
+      <c r="AF57" s="31"/>
+      <c r="AG57" s="31"/>
+      <c r="AH57" s="31"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="26" t="s">
-        <v>520</v>
-      </c>
-      <c r="B58" s="27"/>
-      <c r="C58" s="27"/>
-      <c r="D58" s="27"/>
-      <c r="E58" s="27"/>
-      <c r="F58" s="27"/>
-      <c r="G58" s="27"/>
-      <c r="H58" s="27"/>
-      <c r="I58" s="27"/>
-      <c r="J58" s="27"/>
-      <c r="K58" s="27"/>
-      <c r="L58" s="27"/>
-      <c r="M58" s="27"/>
-      <c r="N58" s="27"/>
-      <c r="O58" s="27"/>
-      <c r="P58" s="27"/>
-      <c r="Q58" s="27"/>
-      <c r="R58" s="27"/>
-      <c r="S58" s="27"/>
-      <c r="T58" s="27"/>
-      <c r="U58" s="27"/>
-      <c r="V58" s="27"/>
-      <c r="W58" s="27"/>
-      <c r="X58" s="27"/>
-      <c r="Y58" s="27"/>
-      <c r="Z58" s="27"/>
-      <c r="AA58" s="27"/>
-      <c r="AB58" s="27"/>
-      <c r="AC58" s="27"/>
-      <c r="AD58" s="27"/>
-      <c r="AE58" s="27"/>
-      <c r="AF58" s="27"/>
-      <c r="AG58" s="27"/>
-      <c r="AH58" s="27"/>
+      <c r="A58" s="27" t="s">
+        <v>521</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
+      <c r="D58" s="28"/>
+      <c r="E58" s="28"/>
+      <c r="F58" s="28"/>
+      <c r="G58" s="28"/>
+      <c r="H58" s="28"/>
+      <c r="I58" s="28"/>
+      <c r="J58" s="28"/>
+      <c r="K58" s="28"/>
+      <c r="L58" s="28"/>
+      <c r="M58" s="28"/>
+      <c r="N58" s="28"/>
+      <c r="O58" s="28"/>
+      <c r="P58" s="28"/>
+      <c r="Q58" s="28"/>
+      <c r="R58" s="28"/>
+      <c r="S58" s="28"/>
+      <c r="T58" s="28"/>
+      <c r="U58" s="28"/>
+      <c r="V58" s="28"/>
+      <c r="W58" s="28"/>
+      <c r="X58" s="28"/>
+      <c r="Y58" s="28"/>
+      <c r="Z58" s="28"/>
+      <c r="AA58" s="28"/>
+      <c r="AB58" s="28"/>
+      <c r="AC58" s="28"/>
+      <c r="AD58" s="28"/>
+      <c r="AE58" s="28"/>
+      <c r="AF58" s="28"/>
+      <c r="AG58" s="28"/>
+      <c r="AH58" s="28"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="28" t="s">
-        <v>521</v>
-      </c>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
-      <c r="D59" s="30"/>
-      <c r="E59" s="30"/>
-      <c r="F59" s="30"/>
-      <c r="G59" s="30"/>
-      <c r="H59" s="34">
+      <c r="A59" s="29" t="s">
+        <v>522</v>
+      </c>
+      <c r="B59" s="31"/>
+      <c r="C59" s="31"/>
+      <c r="D59" s="31"/>
+      <c r="E59" s="31"/>
+      <c r="F59" s="31"/>
+      <c r="G59" s="31"/>
+      <c r="H59" s="35">
         <v>-1.49</v>
       </c>
-      <c r="I59" s="31">
+      <c r="I59" s="32">
         <v>0.44</v>
       </c>
-      <c r="J59" s="30"/>
-      <c r="K59" s="30"/>
-      <c r="L59" s="30"/>
-      <c r="M59" s="30"/>
-      <c r="N59" s="30"/>
-      <c r="O59" s="31">
+      <c r="J59" s="31"/>
+      <c r="K59" s="31"/>
+      <c r="L59" s="31"/>
+      <c r="M59" s="31"/>
+      <c r="N59" s="31"/>
+      <c r="O59" s="32">
         <v>0.18</v>
       </c>
-      <c r="P59" s="31">
+      <c r="P59" s="32">
         <v>4.14</v>
       </c>
-      <c r="Q59" s="31">
+      <c r="Q59" s="32">
         <v>0.92</v>
       </c>
-      <c r="R59" s="30"/>
-      <c r="S59" s="34">
+      <c r="R59" s="31"/>
+      <c r="S59" s="35">
         <v>-0.34</v>
       </c>
-      <c r="T59" s="31">
+      <c r="T59" s="32">
         <v>0.4</v>
       </c>
-      <c r="U59" s="31">
+      <c r="U59" s="32">
         <v>1.08</v>
       </c>
-      <c r="V59" s="31">
+      <c r="V59" s="32">
         <v>0.08</v>
       </c>
-      <c r="W59" s="31">
+      <c r="W59" s="32">
         <v>0.35</v>
       </c>
-      <c r="X59" s="31">
+      <c r="X59" s="32">
         <v>0.38</v>
       </c>
-      <c r="Y59" s="34">
+      <c r="Y59" s="35">
         <v>-5.85</v>
       </c>
-      <c r="Z59" s="34">
+      <c r="Z59" s="35">
         <v>-0.6</v>
       </c>
-      <c r="AA59" s="31">
+      <c r="AA59" s="32">
         <v>0.5</v>
       </c>
-      <c r="AB59" s="34">
+      <c r="AB59" s="35">
         <v>-0.9</v>
       </c>
-      <c r="AC59" s="31">
+      <c r="AC59" s="32">
         <v>0.26</v>
       </c>
-      <c r="AD59" s="31">
+      <c r="AD59" s="32">
         <v>1.48</v>
       </c>
-      <c r="AE59" s="31">
+      <c r="AE59" s="32">
         <v>2.92</v>
       </c>
-      <c r="AF59" s="31">
+      <c r="AF59" s="32">
         <v>0.4</v>
       </c>
-      <c r="AG59" s="31">
+      <c r="AG59" s="32">
         <v>0.02</v>
       </c>
-      <c r="AH59" s="30"/>
+      <c r="AH59" s="31"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
-        <v>522</v>
-      </c>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
-      <c r="D60" s="30"/>
-      <c r="E60" s="30"/>
-      <c r="F60" s="30"/>
-      <c r="G60" s="30"/>
-      <c r="H60" s="30"/>
-      <c r="I60" s="30"/>
-      <c r="J60" s="30"/>
-      <c r="K60" s="30"/>
-      <c r="L60" s="30"/>
-      <c r="M60" s="30"/>
-      <c r="N60" s="30"/>
-      <c r="O60" s="30"/>
-      <c r="P60" s="30"/>
-      <c r="Q60" s="30"/>
-      <c r="R60" s="30"/>
-      <c r="S60" s="34">
+      <c r="A60" s="29" t="s">
+        <v>523</v>
+      </c>
+      <c r="B60" s="31"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="31"/>
+      <c r="F60" s="31"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="31"/>
+      <c r="I60" s="31"/>
+      <c r="J60" s="31"/>
+      <c r="K60" s="31"/>
+      <c r="L60" s="31"/>
+      <c r="M60" s="31"/>
+      <c r="N60" s="31"/>
+      <c r="O60" s="31"/>
+      <c r="P60" s="31"/>
+      <c r="Q60" s="31"/>
+      <c r="R60" s="31"/>
+      <c r="S60" s="35">
         <v>-1.33</v>
       </c>
-      <c r="T60" s="31">
+      <c r="T60" s="32">
         <v>0.29</v>
       </c>
-      <c r="U60" s="31">
+      <c r="U60" s="32">
         <v>0.39</v>
       </c>
-      <c r="V60" s="31">
+      <c r="V60" s="32">
         <v>0.74</v>
       </c>
-      <c r="W60" s="31">
+      <c r="W60" s="32">
         <v>2.03</v>
       </c>
-      <c r="X60" s="34">
+      <c r="X60" s="35">
         <v>-2.39</v>
       </c>
-      <c r="Y60" s="34">
+      <c r="Y60" s="35">
         <v>-8.42</v>
       </c>
-      <c r="Z60" s="31">
+      <c r="Z60" s="32">
         <v>12.6</v>
       </c>
-      <c r="AA60" s="31">
+      <c r="AA60" s="32">
         <v>1.67</v>
       </c>
-      <c r="AB60" s="31">
+      <c r="AB60" s="32">
         <v>1.62</v>
       </c>
-      <c r="AC60" s="31">
+      <c r="AC60" s="32">
         <v>0.21</v>
       </c>
-      <c r="AD60" s="30"/>
-      <c r="AE60" s="30"/>
-      <c r="AF60" s="30"/>
-      <c r="AG60" s="30"/>
-      <c r="AH60" s="30"/>
+      <c r="AD60" s="31"/>
+      <c r="AE60" s="31"/>
+      <c r="AF60" s="31"/>
+      <c r="AG60" s="31"/>
+      <c r="AH60" s="31"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="26" t="s">
-        <v>523</v>
-      </c>
-      <c r="B61" s="27"/>
-      <c r="C61" s="27"/>
-      <c r="D61" s="27"/>
-      <c r="E61" s="27"/>
-      <c r="F61" s="27"/>
-      <c r="G61" s="27"/>
-      <c r="H61" s="27"/>
-      <c r="I61" s="27"/>
-      <c r="J61" s="27"/>
-      <c r="K61" s="27"/>
-      <c r="L61" s="27"/>
-      <c r="M61" s="27"/>
-      <c r="N61" s="27"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="27"/>
-      <c r="Q61" s="27"/>
-      <c r="R61" s="27"/>
-      <c r="S61" s="27"/>
-      <c r="T61" s="27"/>
-      <c r="U61" s="27"/>
-      <c r="V61" s="27"/>
-      <c r="W61" s="27"/>
-      <c r="X61" s="27"/>
-      <c r="Y61" s="27"/>
-      <c r="Z61" s="27"/>
-      <c r="AA61" s="27"/>
-      <c r="AB61" s="27"/>
-      <c r="AC61" s="27"/>
-      <c r="AD61" s="27"/>
-      <c r="AE61" s="27"/>
-      <c r="AF61" s="27"/>
-      <c r="AG61" s="27"/>
-      <c r="AH61" s="27"/>
+      <c r="A61" s="27" t="s">
+        <v>524</v>
+      </c>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
+      <c r="D61" s="28"/>
+      <c r="E61" s="28"/>
+      <c r="F61" s="28"/>
+      <c r="G61" s="28"/>
+      <c r="H61" s="28"/>
+      <c r="I61" s="28"/>
+      <c r="J61" s="28"/>
+      <c r="K61" s="28"/>
+      <c r="L61" s="28"/>
+      <c r="M61" s="28"/>
+      <c r="N61" s="28"/>
+      <c r="O61" s="28"/>
+      <c r="P61" s="28"/>
+      <c r="Q61" s="28"/>
+      <c r="R61" s="28"/>
+      <c r="S61" s="28"/>
+      <c r="T61" s="28"/>
+      <c r="U61" s="28"/>
+      <c r="V61" s="28"/>
+      <c r="W61" s="28"/>
+      <c r="X61" s="28"/>
+      <c r="Y61" s="28"/>
+      <c r="Z61" s="28"/>
+      <c r="AA61" s="28"/>
+      <c r="AB61" s="28"/>
+      <c r="AC61" s="28"/>
+      <c r="AD61" s="28"/>
+      <c r="AE61" s="28"/>
+      <c r="AF61" s="28"/>
+      <c r="AG61" s="28"/>
+      <c r="AH61" s="28"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="28" t="s">
-        <v>524</v>
-      </c>
-      <c r="B62" s="31">
+      <c r="A62" s="29" t="s">
+        <v>525</v>
+      </c>
+      <c r="B62" s="32">
         <v>0.7</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="32">
         <v>0.51</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="32">
         <v>0.49</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="32">
         <v>0.66</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="32">
         <v>1.35</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="32">
         <v>0.53</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="32">
         <v>0.64</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="32">
         <v>1.5</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="32">
         <v>1.2</v>
       </c>
-      <c r="K62" s="31">
+      <c r="K62" s="32">
         <v>0.82</v>
       </c>
-      <c r="L62" s="31">
+      <c r="L62" s="32">
         <v>0.73</v>
       </c>
-      <c r="M62" s="31">
+      <c r="M62" s="32">
         <v>1.31</v>
       </c>
-      <c r="N62" s="31">
+      <c r="N62" s="32">
         <v>0.88</v>
       </c>
-      <c r="O62" s="31">
+      <c r="O62" s="32">
         <v>0.82</v>
       </c>
-      <c r="P62" s="31">
+      <c r="P62" s="32">
         <v>0.93</v>
       </c>
-      <c r="Q62" s="31">
+      <c r="Q62" s="32">
         <v>0.77</v>
       </c>
-      <c r="R62" s="31">
+      <c r="R62" s="32">
         <v>0.62</v>
       </c>
-      <c r="S62" s="31">
+      <c r="S62" s="32">
         <v>0.8</v>
       </c>
-      <c r="T62" s="31">
+      <c r="T62" s="32">
         <v>1.77</v>
       </c>
-      <c r="U62" s="31">
+      <c r="U62" s="32">
         <v>1.78</v>
       </c>
-      <c r="V62" s="31">
+      <c r="V62" s="32">
         <v>1.05</v>
       </c>
-      <c r="W62" s="31">
+      <c r="W62" s="32">
         <v>1.17</v>
       </c>
-      <c r="X62" s="31">
+      <c r="X62" s="32">
         <v>0.47</v>
       </c>
-      <c r="Y62" s="31">
+      <c r="Y62" s="32">
         <v>0.76</v>
       </c>
-      <c r="Z62" s="31">
+      <c r="Z62" s="32">
         <v>0.99</v>
       </c>
-      <c r="AA62" s="31">
+      <c r="AA62" s="32">
         <v>1.02</v>
       </c>
-      <c r="AB62" s="31">
+      <c r="AB62" s="32">
         <v>1.72</v>
       </c>
-      <c r="AC62" s="31">
+      <c r="AC62" s="32">
         <v>1.6</v>
       </c>
-      <c r="AD62" s="31">
+      <c r="AD62" s="32">
         <v>1.45</v>
       </c>
-      <c r="AE62" s="31">
+      <c r="AE62" s="32">
         <v>0.82</v>
       </c>
-      <c r="AF62" s="31">
+      <c r="AF62" s="32">
         <v>0.64</v>
       </c>
-      <c r="AG62" s="31">
+      <c r="AG62" s="32">
         <v>0.48</v>
       </c>
-      <c r="AH62" s="31">
+      <c r="AH62" s="32">
         <v>0.36</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
-        <v>525</v>
-      </c>
-      <c r="B63" s="31">
+      <c r="A63" s="29" t="s">
+        <v>526</v>
+      </c>
+      <c r="B63" s="32">
         <v>0.74</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="32">
         <v>0.71</v>
       </c>
-      <c r="D63" s="31">
+      <c r="D63" s="32">
         <v>0.74</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="32">
         <v>0.97</v>
       </c>
-      <c r="F63" s="31">
+      <c r="F63" s="32">
         <v>1.09</v>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="32">
         <v>0.99</v>
       </c>
-      <c r="H63" s="31">
+      <c r="H63" s="32">
         <v>1.01</v>
       </c>
-      <c r="I63" s="31">
+      <c r="I63" s="32">
         <v>1.14</v>
       </c>
-      <c r="J63" s="31">
+      <c r="J63" s="32">
         <v>0.99</v>
       </c>
-      <c r="K63" s="31">
+      <c r="K63" s="32">
         <v>0.9</v>
       </c>
-      <c r="L63" s="31">
+      <c r="L63" s="32">
         <v>0.92</v>
       </c>
-      <c r="M63" s="31">
+      <c r="M63" s="32">
         <v>0.92</v>
       </c>
-      <c r="N63" s="31">
+      <c r="N63" s="32">
         <v>0.81</v>
       </c>
-      <c r="O63" s="31">
+      <c r="O63" s="32">
         <v>0.79</v>
       </c>
-      <c r="P63" s="31">
+      <c r="P63" s="32">
         <v>1.04</v>
       </c>
-      <c r="Q63" s="31">
+      <c r="Q63" s="32">
         <v>1.23</v>
       </c>
-      <c r="R63" s="31">
+      <c r="R63" s="32">
         <v>1.26</v>
       </c>
-      <c r="S63" s="31">
+      <c r="S63" s="32">
         <v>1.33</v>
       </c>
-      <c r="T63" s="31">
+      <c r="T63" s="32">
         <v>1.27</v>
       </c>
-      <c r="U63" s="31">
+      <c r="U63" s="32">
         <v>1.05</v>
       </c>
-      <c r="V63" s="31">
+      <c r="V63" s="32">
         <v>0.88</v>
       </c>
-      <c r="W63" s="31">
+      <c r="W63" s="32">
         <v>0.87</v>
       </c>
-      <c r="X63" s="31">
+      <c r="X63" s="32">
         <v>0.97</v>
       </c>
-      <c r="Y63" s="31">
+      <c r="Y63" s="32">
         <v>1.18</v>
       </c>
-      <c r="Z63" s="31">
+      <c r="Z63" s="32">
         <v>1.34</v>
       </c>
-      <c r="AA63" s="31">
+      <c r="AA63" s="32">
         <v>1.33</v>
       </c>
-      <c r="AB63" s="31">
+      <c r="AB63" s="32">
         <v>1.28</v>
       </c>
-      <c r="AC63" s="31">
+      <c r="AC63" s="32">
         <v>1.04</v>
       </c>
-      <c r="AD63" s="31">
+      <c r="AD63" s="32">
         <v>0.79</v>
       </c>
-      <c r="AE63" s="30"/>
-      <c r="AF63" s="30"/>
-      <c r="AG63" s="30"/>
-      <c r="AH63" s="30"/>
+      <c r="AE63" s="31"/>
+      <c r="AF63" s="31"/>
+      <c r="AG63" s="31"/>
+      <c r="AH63" s="31"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="26" t="s">
-        <v>526</v>
-      </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="27"/>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="27"/>
-      <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-      <c r="U64" s="27"/>
-      <c r="V64" s="27"/>
-      <c r="W64" s="27"/>
-      <c r="X64" s="27"/>
-      <c r="Y64" s="27"/>
-      <c r="Z64" s="27"/>
-      <c r="AA64" s="27"/>
-      <c r="AB64" s="27"/>
-      <c r="AC64" s="27"/>
-      <c r="AD64" s="27"/>
-      <c r="AE64" s="27"/>
-      <c r="AF64" s="27"/>
-      <c r="AG64" s="27"/>
-      <c r="AH64" s="27"/>
+      <c r="A64" s="27" t="s">
+        <v>527</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
+      <c r="F64" s="28"/>
+      <c r="G64" s="28"/>
+      <c r="H64" s="28"/>
+      <c r="I64" s="28"/>
+      <c r="J64" s="28"/>
+      <c r="K64" s="28"/>
+      <c r="L64" s="28"/>
+      <c r="M64" s="28"/>
+      <c r="N64" s="28"/>
+      <c r="O64" s="28"/>
+      <c r="P64" s="28"/>
+      <c r="Q64" s="28"/>
+      <c r="R64" s="28"/>
+      <c r="S64" s="28"/>
+      <c r="T64" s="28"/>
+      <c r="U64" s="28"/>
+      <c r="V64" s="28"/>
+      <c r="W64" s="28"/>
+      <c r="X64" s="28"/>
+      <c r="Y64" s="28"/>
+      <c r="Z64" s="28"/>
+      <c r="AA64" s="28"/>
+      <c r="AB64" s="28"/>
+      <c r="AC64" s="28"/>
+      <c r="AD64" s="28"/>
+      <c r="AE64" s="28"/>
+      <c r="AF64" s="28"/>
+      <c r="AG64" s="28"/>
+      <c r="AH64" s="28"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="28" t="s">
-        <v>527</v>
-      </c>
-      <c r="B65" s="31">
+      <c r="A65" s="29" t="s">
+        <v>528</v>
+      </c>
+      <c r="B65" s="32">
         <v>6.83</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="32">
         <v>4.75</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="32">
         <v>11.06</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="32">
         <v>7.12</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="32">
         <v>16.03</v>
       </c>
-      <c r="G65" s="30"/>
-      <c r="H65" s="31">
+      <c r="G65" s="31"/>
+      <c r="H65" s="32">
         <v>7.33</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="32">
         <v>12.45</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="32">
         <v>20.61</v>
       </c>
-      <c r="K65" s="31">
+      <c r="K65" s="32">
         <v>52.95</v>
       </c>
-      <c r="L65" s="30"/>
-      <c r="M65" s="31">
+      <c r="L65" s="31"/>
+      <c r="M65" s="32">
         <v>33.51</v>
       </c>
-      <c r="N65" s="31">
+      <c r="N65" s="32">
         <v>17.22</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="32">
         <v>4.03</v>
       </c>
-      <c r="P65" s="31">
+      <c r="P65" s="32">
         <v>7.67</v>
       </c>
-      <c r="Q65" s="31">
+      <c r="Q65" s="32">
         <v>10.67</v>
       </c>
-      <c r="R65" s="30"/>
-      <c r="S65" s="31">
+      <c r="R65" s="31"/>
+      <c r="S65" s="32">
         <v>6.59</v>
       </c>
-      <c r="T65" s="31">
+      <c r="T65" s="32">
         <v>9.96</v>
       </c>
-      <c r="U65" s="31">
+      <c r="U65" s="32">
         <v>11.23</v>
       </c>
-      <c r="V65" s="31">
+      <c r="V65" s="32">
         <v>6.35</v>
       </c>
-      <c r="W65" s="31">
+      <c r="W65" s="32">
         <v>6.79</v>
       </c>
-      <c r="X65" s="31">
+      <c r="X65" s="32">
         <v>3.37</v>
       </c>
-      <c r="Y65" s="31">
+      <c r="Y65" s="32">
         <v>6.09</v>
       </c>
-      <c r="Z65" s="31">
+      <c r="Z65" s="32">
         <v>8.55</v>
       </c>
-      <c r="AA65" s="31">
+      <c r="AA65" s="32">
         <v>8.01</v>
       </c>
-      <c r="AB65" s="31">
+      <c r="AB65" s="32">
         <v>11.2</v>
       </c>
-      <c r="AC65" s="31">
+      <c r="AC65" s="32">
         <v>11.99</v>
       </c>
-      <c r="AD65" s="31">
+      <c r="AD65" s="32">
         <v>10.32</v>
       </c>
-      <c r="AE65" s="31">
+      <c r="AE65" s="32">
         <v>6.17</v>
       </c>
-      <c r="AF65" s="31">
+      <c r="AF65" s="32">
         <v>3.98</v>
       </c>
-      <c r="AG65" s="31">
+      <c r="AG65" s="32">
         <v>3.93</v>
       </c>
-      <c r="AH65" s="31">
+      <c r="AH65" s="32">
         <v>4.97</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
-        <v>528</v>
-      </c>
-      <c r="B66" s="31">
+      <c r="A66" s="29" t="s">
+        <v>529</v>
+      </c>
+      <c r="B66" s="32">
         <v>8.62</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="32">
         <v>11.73</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="32">
         <v>12.82</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="32">
         <v>12.89</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="32">
         <v>15.98</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="32">
         <v>17.97</v>
       </c>
-      <c r="H66" s="31">
+      <c r="H66" s="32">
         <v>30.86</v>
       </c>
-      <c r="I66" s="31">
+      <c r="I66" s="32">
         <v>51.45</v>
       </c>
-      <c r="J66" s="29">
+      <c r="J66" s="30">
         <v>302.45</v>
       </c>
-      <c r="K66" s="31">
+      <c r="K66" s="32">
         <v>24.03</v>
       </c>
-      <c r="L66" s="31">
+      <c r="L66" s="32">
         <v>15.34</v>
       </c>
-      <c r="M66" s="31">
+      <c r="M66" s="32">
         <v>9.04</v>
       </c>
-      <c r="N66" s="30"/>
-      <c r="O66" s="30"/>
-      <c r="P66" s="29">
+      <c r="N66" s="31"/>
+      <c r="O66" s="31"/>
+      <c r="P66" s="30">
         <v>553.44</v>
       </c>
-      <c r="Q66" s="31">
+      <c r="Q66" s="32">
         <v>63.32</v>
       </c>
-      <c r="R66" s="31">
+      <c r="R66" s="32">
         <v>31.38</v>
       </c>
-      <c r="S66" s="31">
+      <c r="S66" s="32">
         <v>8.39</v>
       </c>
-      <c r="T66" s="31">
+      <c r="T66" s="32">
         <v>7.8</v>
       </c>
-      <c r="U66" s="31">
+      <c r="U66" s="32">
         <v>6.93</v>
       </c>
-      <c r="V66" s="31">
+      <c r="V66" s="32">
         <v>6.15</v>
       </c>
-      <c r="W66" s="31">
+      <c r="W66" s="32">
         <v>6.44</v>
       </c>
-      <c r="X66" s="31">
+      <c r="X66" s="32">
         <v>7.34</v>
       </c>
-      <c r="Y66" s="31">
+      <c r="Y66" s="32">
         <v>9.08</v>
       </c>
-      <c r="Z66" s="31">
+      <c r="Z66" s="32">
         <v>10.0</v>
       </c>
-      <c r="AA66" s="31">
+      <c r="AA66" s="32">
         <v>9.66</v>
       </c>
-      <c r="AB66" s="31">
+      <c r="AB66" s="32">
         <v>8.91</v>
       </c>
-      <c r="AC66" s="31">
+      <c r="AC66" s="32">
         <v>7.52</v>
       </c>
-      <c r="AD66" s="31">
+      <c r="AD66" s="32">
         <v>6.16</v>
       </c>
-      <c r="AE66" s="30"/>
-      <c r="AF66" s="30"/>
-      <c r="AG66" s="30"/>
-      <c r="AH66" s="30"/>
+      <c r="AE66" s="31"/>
+      <c r="AF66" s="31"/>
+      <c r="AG66" s="31"/>
+      <c r="AH66" s="31"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="26" t="s">
-        <v>529</v>
-      </c>
-      <c r="B67" s="27"/>
-      <c r="C67" s="27"/>
-      <c r="D67" s="27"/>
-      <c r="E67" s="27"/>
-      <c r="F67" s="27"/>
-      <c r="G67" s="27"/>
-      <c r="H67" s="27"/>
-      <c r="I67" s="27"/>
-      <c r="J67" s="27"/>
-      <c r="K67" s="27"/>
-      <c r="L67" s="27"/>
-      <c r="M67" s="27"/>
-      <c r="N67" s="27"/>
-      <c r="O67" s="27"/>
-      <c r="P67" s="27"/>
-      <c r="Q67" s="27"/>
-      <c r="R67" s="27"/>
-      <c r="S67" s="27"/>
-      <c r="T67" s="27"/>
-      <c r="U67" s="27"/>
-      <c r="V67" s="27"/>
-      <c r="W67" s="27"/>
-      <c r="X67" s="27"/>
-      <c r="Y67" s="27"/>
-      <c r="Z67" s="27"/>
-      <c r="AA67" s="27"/>
-      <c r="AB67" s="27"/>
-      <c r="AC67" s="27"/>
-      <c r="AD67" s="27"/>
-      <c r="AE67" s="27"/>
-      <c r="AF67" s="27"/>
-      <c r="AG67" s="27"/>
-      <c r="AH67" s="27"/>
+      <c r="A67" s="27" t="s">
+        <v>530</v>
+      </c>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28"/>
+      <c r="H67" s="28"/>
+      <c r="I67" s="28"/>
+      <c r="J67" s="28"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
+      <c r="N67" s="28"/>
+      <c r="O67" s="28"/>
+      <c r="P67" s="28"/>
+      <c r="Q67" s="28"/>
+      <c r="R67" s="28"/>
+      <c r="S67" s="28"/>
+      <c r="T67" s="28"/>
+      <c r="U67" s="28"/>
+      <c r="V67" s="28"/>
+      <c r="W67" s="28"/>
+      <c r="X67" s="28"/>
+      <c r="Y67" s="28"/>
+      <c r="Z67" s="28"/>
+      <c r="AA67" s="28"/>
+      <c r="AB67" s="28"/>
+      <c r="AC67" s="28"/>
+      <c r="AD67" s="28"/>
+      <c r="AE67" s="28"/>
+      <c r="AF67" s="28"/>
+      <c r="AG67" s="28"/>
+      <c r="AH67" s="28"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="28" t="s">
-        <v>530</v>
-      </c>
-      <c r="B68" s="31">
+      <c r="A68" s="29" t="s">
+        <v>531</v>
+      </c>
+      <c r="B68" s="32">
         <v>7.04</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="32">
         <v>5.75</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="32">
         <v>6.87</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="32">
         <v>25.5</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="32">
         <v>11.98</v>
       </c>
-      <c r="G68" s="30"/>
-      <c r="H68" s="30"/>
-      <c r="I68" s="31">
+      <c r="G68" s="31"/>
+      <c r="H68" s="31"/>
+      <c r="I68" s="32">
         <v>19.93</v>
       </c>
-      <c r="J68" s="31">
+      <c r="J68" s="32">
         <v>10.08</v>
       </c>
-      <c r="K68" s="30"/>
-      <c r="L68" s="31">
+      <c r="K68" s="31"/>
+      <c r="L68" s="32">
         <v>31.22</v>
       </c>
-      <c r="M68" s="31">
+      <c r="M68" s="32">
         <v>15.41</v>
       </c>
-      <c r="N68" s="31">
+      <c r="N68" s="32">
         <v>19.44</v>
       </c>
-      <c r="O68" s="31">
+      <c r="O68" s="32">
         <v>11.0</v>
       </c>
-      <c r="P68" s="31">
+      <c r="P68" s="32">
         <v>8.37</v>
       </c>
-      <c r="Q68" s="31">
+      <c r="Q68" s="32">
         <v>9.69</v>
       </c>
-      <c r="R68" s="31">
+      <c r="R68" s="32">
         <v>15.33</v>
       </c>
-      <c r="S68" s="31">
+      <c r="S68" s="32">
         <v>9.81</v>
       </c>
-      <c r="T68" s="31">
+      <c r="T68" s="32">
         <v>14.9</v>
       </c>
-      <c r="U68" s="31">
+      <c r="U68" s="32">
         <v>19.1</v>
       </c>
-      <c r="V68" s="31">
+      <c r="V68" s="32">
         <v>5.28</v>
       </c>
-      <c r="W68" s="31">
+      <c r="W68" s="32">
         <v>9.41</v>
       </c>
-      <c r="X68" s="31">
+      <c r="X68" s="32">
         <v>2.93</v>
       </c>
-      <c r="Y68" s="31">
+      <c r="Y68" s="32">
         <v>7.37</v>
       </c>
-      <c r="Z68" s="31">
+      <c r="Z68" s="32">
         <v>27.48</v>
       </c>
-      <c r="AA68" s="31">
+      <c r="AA68" s="32">
         <v>15.59</v>
       </c>
-      <c r="AB68" s="31">
+      <c r="AB68" s="32">
         <v>19.55</v>
       </c>
-      <c r="AC68" s="31">
+      <c r="AC68" s="32">
         <v>12.68</v>
       </c>
-      <c r="AD68" s="31">
+      <c r="AD68" s="32">
         <v>14.92</v>
       </c>
-      <c r="AE68" s="31">
+      <c r="AE68" s="32">
         <v>7.76</v>
       </c>
-      <c r="AF68" s="31">
+      <c r="AF68" s="32">
         <v>6.85</v>
       </c>
-      <c r="AG68" s="31">
+      <c r="AG68" s="32">
         <v>2.58</v>
       </c>
-      <c r="AH68" s="31">
+      <c r="AH68" s="32">
         <v>3.6</v>
       </c>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
-        <v>531</v>
-      </c>
-      <c r="B69" s="31">
+      <c r="A69" s="29" t="s">
+        <v>532</v>
+      </c>
+      <c r="B69" s="32">
         <v>9.45</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="32">
         <v>12.87</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="32">
         <v>27.14</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="32">
         <v>32.57</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F69" s="32">
         <v>21.8</v>
       </c>
-      <c r="G69" s="31">
+      <c r="G69" s="32">
         <v>35.31</v>
       </c>
-      <c r="H69" s="31">
+      <c r="H69" s="32">
         <v>27.35</v>
       </c>
-      <c r="I69" s="31">
+      <c r="I69" s="32">
         <v>18.23</v>
       </c>
-      <c r="J69" s="31">
+      <c r="J69" s="32">
         <v>17.86</v>
       </c>
-      <c r="K69" s="31">
+      <c r="K69" s="32">
         <v>19.9</v>
       </c>
-      <c r="L69" s="31">
+      <c r="L69" s="32">
         <v>13.36</v>
       </c>
-      <c r="M69" s="31">
+      <c r="M69" s="32">
         <v>11.7</v>
       </c>
-      <c r="N69" s="31">
+      <c r="N69" s="32">
         <v>11.43</v>
       </c>
-      <c r="O69" s="31">
+      <c r="O69" s="32">
         <v>10.14</v>
       </c>
-      <c r="P69" s="31">
+      <c r="P69" s="32">
         <v>11.66</v>
       </c>
-      <c r="Q69" s="31">
+      <c r="Q69" s="32">
         <v>14.19</v>
       </c>
-      <c r="R69" s="31">
+      <c r="R69" s="32">
         <v>11.52</v>
       </c>
-      <c r="S69" s="31">
+      <c r="S69" s="32">
         <v>10.96</v>
       </c>
-      <c r="T69" s="31">
+      <c r="T69" s="32">
         <v>9.22</v>
       </c>
-      <c r="U69" s="31">
+      <c r="U69" s="32">
         <v>7.8</v>
       </c>
-      <c r="V69" s="31">
+      <c r="V69" s="32">
         <v>7.07</v>
       </c>
-      <c r="W69" s="31">
+      <c r="W69" s="32">
         <v>8.86</v>
       </c>
-      <c r="X69" s="31">
+      <c r="X69" s="32">
         <v>10.53</v>
       </c>
-      <c r="Y69" s="31">
+      <c r="Y69" s="32">
         <v>14.34</v>
       </c>
-      <c r="Z69" s="31">
+      <c r="Z69" s="32">
         <v>16.67</v>
       </c>
-      <c r="AA69" s="31">
+      <c r="AA69" s="32">
         <v>14.01</v>
       </c>
-      <c r="AB69" s="31">
+      <c r="AB69" s="32">
         <v>12.59</v>
       </c>
-      <c r="AC69" s="31">
+      <c r="AC69" s="32">
         <v>8.65</v>
       </c>
-      <c r="AD69" s="31">
+      <c r="AD69" s="32">
         <v>6.86</v>
       </c>
-      <c r="AE69" s="30"/>
-      <c r="AF69" s="30"/>
-      <c r="AG69" s="30"/>
-      <c r="AH69" s="30"/>
+      <c r="AE69" s="31"/>
+      <c r="AF69" s="31"/>
+      <c r="AG69" s="31"/>
+      <c r="AH69" s="31"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="26" t="s">
-        <v>532</v>
-      </c>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="27"/>
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="27"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="27"/>
-      <c r="R70" s="27"/>
-      <c r="S70" s="27"/>
-      <c r="T70" s="27"/>
-      <c r="U70" s="27"/>
-      <c r="V70" s="27"/>
-      <c r="W70" s="27"/>
-      <c r="X70" s="27"/>
-      <c r="Y70" s="27"/>
-      <c r="Z70" s="27"/>
-      <c r="AA70" s="27"/>
-      <c r="AB70" s="27"/>
-      <c r="AC70" s="27"/>
-      <c r="AD70" s="27"/>
-      <c r="AE70" s="27"/>
-      <c r="AF70" s="27"/>
-      <c r="AG70" s="27"/>
-      <c r="AH70" s="27"/>
+      <c r="A70" s="27" t="s">
+        <v>533</v>
+      </c>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28"/>
+      <c r="H70" s="28"/>
+      <c r="I70" s="28"/>
+      <c r="J70" s="28"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="28"/>
+      <c r="M70" s="28"/>
+      <c r="N70" s="28"/>
+      <c r="O70" s="28"/>
+      <c r="P70" s="28"/>
+      <c r="Q70" s="28"/>
+      <c r="R70" s="28"/>
+      <c r="S70" s="28"/>
+      <c r="T70" s="28"/>
+      <c r="U70" s="28"/>
+      <c r="V70" s="28"/>
+      <c r="W70" s="28"/>
+      <c r="X70" s="28"/>
+      <c r="Y70" s="28"/>
+      <c r="Z70" s="28"/>
+      <c r="AA70" s="28"/>
+      <c r="AB70" s="28"/>
+      <c r="AC70" s="28"/>
+      <c r="AD70" s="28"/>
+      <c r="AE70" s="28"/>
+      <c r="AF70" s="28"/>
+      <c r="AG70" s="28"/>
+      <c r="AH70" s="28"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="28" t="s">
-        <v>533</v>
-      </c>
-      <c r="B71" s="29">
+      <c r="A71" s="29" t="s">
+        <v>534</v>
+      </c>
+      <c r="B71" s="30">
         <v>112.25</v>
       </c>
-      <c r="C71" s="29">
+      <c r="C71" s="30">
         <v>131.08</v>
       </c>
-      <c r="D71" s="30"/>
-      <c r="E71" s="30"/>
-      <c r="F71" s="31">
+      <c r="D71" s="31"/>
+      <c r="E71" s="31"/>
+      <c r="F71" s="32">
         <v>31.49</v>
       </c>
-      <c r="G71" s="30"/>
-      <c r="H71" s="30"/>
-      <c r="I71" s="31">
+      <c r="G71" s="31"/>
+      <c r="H71" s="31"/>
+      <c r="I71" s="32">
         <v>61.01</v>
       </c>
-      <c r="J71" s="31">
+      <c r="J71" s="32">
         <v>32.12</v>
       </c>
-      <c r="K71" s="30"/>
-      <c r="L71" s="30"/>
-      <c r="M71" s="30"/>
-      <c r="N71" s="30"/>
-      <c r="O71" s="30"/>
-      <c r="P71" s="30"/>
-      <c r="Q71" s="30"/>
-      <c r="R71" s="30"/>
-      <c r="S71" s="29">
+      <c r="K71" s="31"/>
+      <c r="L71" s="31"/>
+      <c r="M71" s="31"/>
+      <c r="N71" s="31"/>
+      <c r="O71" s="31"/>
+      <c r="P71" s="31"/>
+      <c r="Q71" s="31"/>
+      <c r="R71" s="31"/>
+      <c r="S71" s="30">
         <v>197.29</v>
       </c>
-      <c r="T71" s="31">
+      <c r="T71" s="32">
         <v>50.7</v>
       </c>
-      <c r="U71" s="29">
+      <c r="U71" s="30">
         <v>198.3</v>
       </c>
-      <c r="V71" s="31">
+      <c r="V71" s="32">
         <v>7.94</v>
       </c>
-      <c r="W71" s="31">
+      <c r="W71" s="32">
         <v>25.82</v>
       </c>
-      <c r="X71" s="31">
+      <c r="X71" s="32">
         <v>5.16</v>
       </c>
-      <c r="Y71" s="31">
+      <c r="Y71" s="32">
         <v>16.09</v>
       </c>
-      <c r="Z71" s="30"/>
-      <c r="AA71" s="30"/>
-      <c r="AB71" s="31">
+      <c r="Z71" s="31"/>
+      <c r="AA71" s="31"/>
+      <c r="AB71" s="32">
         <v>88.35</v>
       </c>
-      <c r="AC71" s="31">
+      <c r="AC71" s="32">
         <v>28.66</v>
       </c>
-      <c r="AD71" s="31">
+      <c r="AD71" s="32">
         <v>36.25</v>
       </c>
-      <c r="AE71" s="31">
+      <c r="AE71" s="32">
         <v>18.69</v>
       </c>
-      <c r="AF71" s="31">
+      <c r="AF71" s="32">
         <v>12.55</v>
       </c>
-      <c r="AG71" s="31">
+      <c r="AG71" s="32">
         <v>3.25</v>
       </c>
-      <c r="AH71" s="31">
+      <c r="AH71" s="32">
         <v>8.83</v>
       </c>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="28" t="s">
-        <v>534</v>
-      </c>
-      <c r="B72" s="30"/>
-      <c r="C72" s="30"/>
-      <c r="D72" s="30"/>
-      <c r="E72" s="30"/>
-      <c r="F72" s="30"/>
-      <c r="G72" s="30"/>
-      <c r="H72" s="30"/>
-      <c r="I72" s="30"/>
-      <c r="J72" s="30"/>
-      <c r="K72" s="30"/>
-      <c r="L72" s="30"/>
-      <c r="M72" s="30"/>
-      <c r="N72" s="30"/>
-      <c r="O72" s="30"/>
-      <c r="P72" s="30"/>
-      <c r="Q72" s="30"/>
-      <c r="R72" s="31">
+      <c r="A72" s="29" t="s">
+        <v>535</v>
+      </c>
+      <c r="B72" s="31"/>
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
+      <c r="F72" s="31"/>
+      <c r="G72" s="31"/>
+      <c r="H72" s="31"/>
+      <c r="I72" s="31"/>
+      <c r="J72" s="31"/>
+      <c r="K72" s="31"/>
+      <c r="L72" s="31"/>
+      <c r="M72" s="31"/>
+      <c r="N72" s="31"/>
+      <c r="O72" s="31"/>
+      <c r="P72" s="31"/>
+      <c r="Q72" s="31"/>
+      <c r="R72" s="32">
         <v>49.34</v>
       </c>
-      <c r="S72" s="31">
+      <c r="S72" s="32">
         <v>30.9</v>
       </c>
-      <c r="T72" s="31">
+      <c r="T72" s="32">
         <v>20.89</v>
       </c>
-      <c r="U72" s="31">
+      <c r="U72" s="32">
         <v>16.5</v>
       </c>
-      <c r="V72" s="31">
+      <c r="V72" s="32">
         <v>15.72</v>
       </c>
-      <c r="W72" s="31">
+      <c r="W72" s="32">
         <v>32.2</v>
       </c>
-      <c r="X72" s="31">
+      <c r="X72" s="32">
         <v>43.31</v>
       </c>
-      <c r="Y72" s="31">
+      <c r="Y72" s="32">
         <v>91.34</v>
       </c>
-      <c r="Z72" s="29">
+      <c r="Z72" s="30">
         <v>143.72</v>
       </c>
-      <c r="AA72" s="31">
+      <c r="AA72" s="32">
         <v>51.06</v>
       </c>
-      <c r="AB72" s="31">
+      <c r="AB72" s="32">
         <v>31.11</v>
       </c>
-      <c r="AC72" s="31">
+      <c r="AC72" s="32">
         <v>15.96</v>
       </c>
-      <c r="AD72" s="31">
+      <c r="AD72" s="32">
         <v>12.5</v>
       </c>
-      <c r="AE72" s="30"/>
-      <c r="AF72" s="30"/>
-      <c r="AG72" s="30"/>
-      <c r="AH72" s="30"/>
+      <c r="AE72" s="31"/>
+      <c r="AF72" s="31"/>
+      <c r="AG72" s="31"/>
+      <c r="AH72" s="31"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
